--- a/excel-sync/lots_template.xlsx
+++ b/excel-sync/lots_template.xlsx
@@ -49,9 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -136,7 +139,7 @@
   <commentList>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Full local file paths, separated by semicolons, e.g. C:\Photos\a.jpg;C:\Photos\b.jpg</t>
+        <t>One file path per box (Photo 1, Photo 2, ...). Leave extras blank if you have fewer than 5 photos, e.g. C:\Photos\a.jpg</t>
       </text>
     </comment>
   </commentList>
@@ -432,8 +435,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="60"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -441,11 +444,15 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="60" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="60" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="60" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,25 +488,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Photo Paths</t>
+          <t>Photo 1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Photo 2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Photo 3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Photo 4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Photo 5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Last Synced</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Last Synced Fingerprint</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Last Synced Photo Paths</t>
         </is>
@@ -521,9 +548,9 @@
           <t>Peace Dollar Lot (38 coins)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>38 common-date silver dollars, cleaned. Melt value checked by hand before pricing.</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>38 common-date silver dollars, cleaned by hand. Melt value checked against spot price before setting the website price -- do not price below melt.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -536,9 +563,615 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Photos\A1234-a.jpg;C:\Photos\A1234-b.jpg</t>
-        </is>
-      </c>
+          <t>C:\Photos\A1234-a.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>C:\Photos\A1234-b.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/excel-sync/lots_template.xlsx
+++ b/excel-sync/lots_template.xlsx
@@ -9,15 +9,19 @@
   <sheets>
     <sheet name="Lots" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lots'!$A$1:$R$200</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +32,54 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A8A296"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003F5738"/>
+        <bgColor rgb="003F5738"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A6512B"/>
+        <bgColor rgb="00A6512B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A8478"/>
+        <bgColor rgb="008A8478"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF6ED"/>
+        <bgColor rgb="00FAF6ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7B0A0"/>
+        <bgColor rgb="00B7B0A0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,20 +87,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D8CFC0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8CFC0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8CFC0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8CFC0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FAF6ED"/>
+          <bgColor rgb="00FAF6ED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D6F5F2"/>
+          <bgColor rgb="00D6F5F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F5E6C8"/>
+          <bgColor rgb="00F5E6C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8E4DC"/>
+          <bgColor rgb="00E8E4DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCE0F0"/>
+          <bgColor rgb="00DCE0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -134,10 +249,16 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Holly Hill</author>
     <author>Holly Hill Surplus</author>
   </authors>
   <commentList>
     <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Private -- stays in this spreadsheet only, never sent to the website.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="1" shapeId="0">
       <text>
         <t>One file path per box (Photo 1, Photo 2, ...). Leave extras blank if you have fewer than 5 photos, e.g. C:\Photos\a.jpg</t>
       </text>
@@ -435,745 +556,5361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:U200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="60"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="60" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="60" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="60" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="60" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Lot # / SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Price ($)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Original Price ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Profit ($)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Featured</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Photo 1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Photo 2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Photo 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Photo 4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Photo 5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Last Synced</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Last Synced Fingerprint</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Last Synced Photo Paths</t>
         </is>
       </c>
+      <c r="T1" s="12" t="inlineStr">
+        <is>
+          <t>Feature Count:</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>EXAMPLE — delete this row</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Coins &amp; Currency</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Peace Dollar Lot (38 coins)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>38 common-date silver dollars, cleaned by hand. Melt value checked against spot price before setting the website price -- do not price below melt.</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="7" t="n">
         <v>1325</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14">
+        <f>IF(G2="","",E2-G2)</f>
+        <v/>
+      </c>
+      <c r="I2" s="7">
+        <f>IF(AND(F2="available",G2&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H2)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>C:\Photos\A1234-a.jpg</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>C:\Photos\A1234-b.jpg</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="7" t="n"/>
+      <c r="O2" s="7" t="n"/>
+      <c r="P2" s="7" t="n"/>
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="D3" s="2" t="n"/>
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15">
+        <f>IF(G3="","",E3-G3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="9">
+        <f>IF(AND(F3="available",G3&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H3)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="9" t="n"/>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="9" t="n"/>
+      <c r="P3" s="9" t="n"/>
+      <c r="Q3" s="9" t="n"/>
+      <c r="R3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="D4" s="2" t="n"/>
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15">
+        <f>IF(G4="","",E4-G4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="9">
+        <f>IF(AND(F4="available",G4&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H4)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="D5" s="2" t="n"/>
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15">
+        <f>IF(G5="","",E5-G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="9">
+        <f>IF(AND(F5="available",G5&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H5)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" s="2" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15">
+        <f>IF(G6="","",E6-G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>IF(AND(F6="available",G6&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H6)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" s="2" t="n"/>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15">
+        <f>IF(G7="","",E7-G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>IF(AND(F7="available",G7&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H7)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" s="2" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15">
+        <f>IF(G8="","",E8-G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>IF(AND(F8="available",G8&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H8)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="2" t="n"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15">
+        <f>IF(G9="","",E9-G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(AND(F9="available",G9&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H9)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" s="2" t="n"/>
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15">
+        <f>IF(G10="","",E10-G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>IF(AND(F10="available",G10&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H10)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" s="2" t="n"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15">
+        <f>IF(G11="","",E11-G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>IF(AND(F11="available",G11&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H11)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="D12" s="2" t="n"/>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15">
+        <f>IF(G12="","",E12-G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>IF(AND(F12="available",G12&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H12)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="D13" s="2" t="n"/>
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15">
+        <f>IF(G13="","",E13-G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>IF(AND(F13="available",G13&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H13)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="D14" s="2" t="n"/>
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15">
+        <f>IF(G14="","",E14-G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>IF(AND(F14="available",G14&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H14)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="D15" s="2" t="n"/>
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15">
+        <f>IF(G15="","",E15-G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>IF(AND(F15="available",G15&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H15)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="D16" s="2" t="n"/>
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15">
+        <f>IF(G16="","",E16-G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>IF(AND(F16="available",G16&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H16)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="D17" s="2" t="n"/>
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15">
+        <f>IF(G17="","",E17-G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>IF(AND(F17="available",G17&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H17)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="D18" s="2" t="n"/>
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15">
+        <f>IF(G18="","",E18-G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="9">
+        <f>IF(AND(F18="available",G18&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H18)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="D19" s="2" t="n"/>
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15">
+        <f>IF(G19="","",E19-G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>IF(AND(F19="available",G19&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H19)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="D20" s="2" t="n"/>
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15">
+        <f>IF(G20="","",E20-G20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>IF(AND(F20="available",G20&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H20)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="D21" s="2" t="n"/>
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15">
+        <f>IF(G21="","",E21-G21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="9">
+        <f>IF(AND(F21="available",G21&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H21)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="2" t="n"/>
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15">
+        <f>IF(G22="","",E22-G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>IF(AND(F22="available",G22&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H22)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="D23" s="2" t="n"/>
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15">
+        <f>IF(G23="","",E23-G23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>IF(AND(F23="available",G23&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H23)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="2" t="n"/>
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15">
+        <f>IF(G24="","",E24-G24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="9">
+        <f>IF(AND(F24="available",G24&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H24)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="D25" s="2" t="n"/>
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15">
+        <f>IF(G25="","",E25-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>IF(AND(F25="available",G25&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H25)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="D26" s="2" t="n"/>
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15">
+        <f>IF(G26="","",E26-G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>IF(AND(F26="available",G26&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H26)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="D27" s="2" t="n"/>
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15">
+        <f>IF(G27="","",E27-G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>IF(AND(F27="available",G27&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H27)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="2" t="n"/>
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15">
+        <f>IF(G28="","",E28-G28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>IF(AND(F28="available",G28&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H28)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="D29" s="2" t="n"/>
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15">
+        <f>IF(G29="","",E29-G29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>IF(AND(F29="available",G29&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H29)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="D30" s="2" t="n"/>
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15">
+        <f>IF(G30="","",E30-G30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>IF(AND(F30="available",G30&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H30)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="D31" s="2" t="n"/>
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15">
+        <f>IF(G31="","",E31-G31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IF(AND(F31="available",G31&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H31)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="D32" s="2" t="n"/>
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15">
+        <f>IF(G32="","",E32-G32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>IF(AND(F32="available",G32&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H32)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="2" t="n"/>
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15">
+        <f>IF(G33="","",E33-G33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>IF(AND(F33="available",G33&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H33)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="D34" s="2" t="n"/>
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15">
+        <f>IF(G34="","",E34-G34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>IF(AND(F34="available",G34&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H34)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="D35" s="2" t="n"/>
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15">
+        <f>IF(G35="","",E35-G35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>IF(AND(F35="available",G35&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H35)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="D36" s="2" t="n"/>
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15">
+        <f>IF(G36="","",E36-G36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>IF(AND(F36="available",G36&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H36)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="D37" s="2" t="n"/>
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15">
+        <f>IF(G37="","",E37-G37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>IF(AND(F37="available",G37&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H37)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="D38" s="2" t="n"/>
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15">
+        <f>IF(G38="","",E38-G38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>IF(AND(F38="available",G38&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H38)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="2" t="n"/>
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15">
+        <f>IF(G39="","",E39-G39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>IF(AND(F39="available",G39&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H39)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="D40" s="2" t="n"/>
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15">
+        <f>IF(G40="","",E40-G40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="9">
+        <f>IF(AND(F40="available",G40&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H40)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="D41" s="2" t="n"/>
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15">
+        <f>IF(G41="","",E41-G41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="9">
+        <f>IF(AND(F41="available",G41&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H41)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="2" t="n"/>
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15">
+        <f>IF(G42="","",E42-G42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="9">
+        <f>IF(AND(F42="available",G42&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H42)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="2" t="n"/>
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15">
+        <f>IF(G43="","",E43-G43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="9">
+        <f>IF(AND(F43="available",G43&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H43)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="9" t="n"/>
     </row>
     <row r="44">
-      <c r="D44" s="2" t="n"/>
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15">
+        <f>IF(G44="","",E44-G44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="9">
+        <f>IF(AND(F44="available",G44&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H44)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="9" t="n"/>
+      <c r="R44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="D45" s="2" t="n"/>
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15">
+        <f>IF(G45="","",E45-G45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="9">
+        <f>IF(AND(F45="available",G45&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H45)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="2" t="n"/>
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15">
+        <f>IF(G46="","",E46-G46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="9">
+        <f>IF(AND(F46="available",G46&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H46)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="9" t="n"/>
+      <c r="Q46" s="9" t="n"/>
+      <c r="R46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="2" t="n"/>
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15">
+        <f>IF(G47="","",E47-G47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="9">
+        <f>IF(AND(F47="available",G47&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H47)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="2" t="n"/>
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15">
+        <f>IF(G48="","",E48-G48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="9">
+        <f>IF(AND(F48="available",G48&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H48)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="9" t="n"/>
+      <c r="Q48" s="9" t="n"/>
+      <c r="R48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="2" t="n"/>
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15">
+        <f>IF(G49="","",E49-G49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="9">
+        <f>IF(AND(F49="available",G49&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H49)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="2" t="n"/>
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15">
+        <f>IF(G50="","",E50-G50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="9">
+        <f>IF(AND(F50="available",G50&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H50)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="2" t="n"/>
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15">
+        <f>IF(G51="","",E51-G51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="9">
+        <f>IF(AND(F51="available",G51&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H51)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="9" t="n"/>
     </row>
     <row r="52">
-      <c r="D52" s="2" t="n"/>
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15">
+        <f>IF(G52="","",E52-G52)</f>
+        <v/>
+      </c>
+      <c r="I52" s="9">
+        <f>IF(AND(F52="available",G52&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H52)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n"/>
+      <c r="R52" s="9" t="n"/>
     </row>
     <row r="53">
-      <c r="D53" s="2" t="n"/>
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15">
+        <f>IF(G53="","",E53-G53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="9">
+        <f>IF(AND(F53="available",G53&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H53)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="2" t="n"/>
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15">
+        <f>IF(G54="","",E54-G54)</f>
+        <v/>
+      </c>
+      <c r="I54" s="9">
+        <f>IF(AND(F54="available",G54&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H54)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="9" t="n"/>
     </row>
     <row r="55">
-      <c r="D55" s="2" t="n"/>
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15">
+        <f>IF(G55="","",E55-G55)</f>
+        <v/>
+      </c>
+      <c r="I55" s="9">
+        <f>IF(AND(F55="available",G55&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H55)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="D56" s="2" t="n"/>
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="15">
+        <f>IF(G56="","",E56-G56)</f>
+        <v/>
+      </c>
+      <c r="I56" s="9">
+        <f>IF(AND(F56="available",G56&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H56)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="9" t="n"/>
     </row>
     <row r="57">
-      <c r="D57" s="2" t="n"/>
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="15">
+        <f>IF(G57="","",E57-G57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="9">
+        <f>IF(AND(F57="available",G57&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H57)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="9" t="n"/>
     </row>
     <row r="58">
-      <c r="D58" s="2" t="n"/>
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15">
+        <f>IF(G58="","",E58-G58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="9">
+        <f>IF(AND(F58="available",G58&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H58)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="9" t="n"/>
     </row>
     <row r="59">
-      <c r="D59" s="2" t="n"/>
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="15">
+        <f>IF(G59="","",E59-G59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="9">
+        <f>IF(AND(F59="available",G59&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H59)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="9" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="9" t="n"/>
     </row>
     <row r="60">
-      <c r="D60" s="2" t="n"/>
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="15">
+        <f>IF(G60="","",E60-G60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="9">
+        <f>IF(AND(F60="available",G60&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H60)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J60" s="9" t="n"/>
+      <c r="K60" s="9" t="n"/>
+      <c r="L60" s="9" t="n"/>
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="9" t="n"/>
+      <c r="Q60" s="9" t="n"/>
+      <c r="R60" s="9" t="n"/>
     </row>
     <row r="61">
-      <c r="D61" s="2" t="n"/>
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="15" t="n"/>
+      <c r="H61" s="15">
+        <f>IF(G61="","",E61-G61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="9">
+        <f>IF(AND(F61="available",G61&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H61)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="9" t="n"/>
     </row>
     <row r="62">
-      <c r="D62" s="2" t="n"/>
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15">
+        <f>IF(G62="","",E62-G62)</f>
+        <v/>
+      </c>
+      <c r="I62" s="9">
+        <f>IF(AND(F62="available",G62&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H62)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="n"/>
+      <c r="M62" s="9" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="9" t="n"/>
     </row>
     <row r="63">
-      <c r="D63" s="2" t="n"/>
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="15" t="n"/>
+      <c r="H63" s="15">
+        <f>IF(G63="","",E63-G63)</f>
+        <v/>
+      </c>
+      <c r="I63" s="9">
+        <f>IF(AND(F63="available",G63&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H63)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="9" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="2" t="n"/>
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="15" t="n"/>
+      <c r="H64" s="15">
+        <f>IF(G64="","",E64-G64)</f>
+        <v/>
+      </c>
+      <c r="I64" s="9">
+        <f>IF(AND(F64="available",G64&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H64)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J64" s="9" t="n"/>
+      <c r="K64" s="9" t="n"/>
+      <c r="L64" s="9" t="n"/>
+      <c r="M64" s="9" t="n"/>
+      <c r="N64" s="9" t="n"/>
+      <c r="O64" s="9" t="n"/>
+      <c r="P64" s="9" t="n"/>
+      <c r="Q64" s="9" t="n"/>
+      <c r="R64" s="9" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="2" t="n"/>
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="15" t="n"/>
+      <c r="H65" s="15">
+        <f>IF(G65="","",E65-G65)</f>
+        <v/>
+      </c>
+      <c r="I65" s="9">
+        <f>IF(AND(F65="available",G65&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H65)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="2" t="n"/>
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="15">
+        <f>IF(G66="","",E66-G66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="9">
+        <f>IF(AND(F66="available",G66&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H66)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
+      <c r="L66" s="9" t="n"/>
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
+      <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="9" t="n"/>
     </row>
     <row r="67">
-      <c r="D67" s="2" t="n"/>
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="15">
+        <f>IF(G67="","",E67-G67)</f>
+        <v/>
+      </c>
+      <c r="I67" s="9">
+        <f>IF(AND(F67="available",G67&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H67)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J67" s="9" t="n"/>
+      <c r="K67" s="9" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="9" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="2" t="n"/>
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="15">
+        <f>IF(G68="","",E68-G68)</f>
+        <v/>
+      </c>
+      <c r="I68" s="9">
+        <f>IF(AND(F68="available",G68&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H68)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="9" t="n"/>
+      <c r="L68" s="9" t="n"/>
+      <c r="M68" s="9" t="n"/>
+      <c r="N68" s="9" t="n"/>
+      <c r="O68" s="9" t="n"/>
+      <c r="P68" s="9" t="n"/>
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="9" t="n"/>
     </row>
     <row r="69">
-      <c r="D69" s="2" t="n"/>
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15">
+        <f>IF(G69="","",E69-G69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="9">
+        <f>IF(AND(F69="available",G69&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H69)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
     </row>
     <row r="70">
-      <c r="D70" s="2" t="n"/>
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="15">
+        <f>IF(G70="","",E70-G70)</f>
+        <v/>
+      </c>
+      <c r="I70" s="9">
+        <f>IF(AND(F70="available",G70&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H70)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
+      <c r="L70" s="9" t="n"/>
+      <c r="M70" s="9" t="n"/>
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="D71" s="2" t="n"/>
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="15" t="n"/>
+      <c r="H71" s="15">
+        <f>IF(G71="","",E71-G71)</f>
+        <v/>
+      </c>
+      <c r="I71" s="9">
+        <f>IF(AND(F71="available",G71&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H71)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J71" s="9" t="n"/>
+      <c r="K71" s="9" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="9" t="n"/>
     </row>
     <row r="72">
-      <c r="D72" s="2" t="n"/>
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="15">
+        <f>IF(G72="","",E72-G72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="9">
+        <f>IF(AND(F72="available",G72&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H72)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="9" t="n"/>
+      <c r="L72" s="9" t="n"/>
+      <c r="M72" s="9" t="n"/>
+      <c r="N72" s="9" t="n"/>
+      <c r="O72" s="9" t="n"/>
+      <c r="P72" s="9" t="n"/>
+      <c r="Q72" s="9" t="n"/>
+      <c r="R72" s="9" t="n"/>
     </row>
     <row r="73">
-      <c r="D73" s="2" t="n"/>
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="15" t="n"/>
+      <c r="H73" s="15">
+        <f>IF(G73="","",E73-G73)</f>
+        <v/>
+      </c>
+      <c r="I73" s="9">
+        <f>IF(AND(F73="available",G73&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H73)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="9" t="n"/>
     </row>
     <row r="74">
-      <c r="D74" s="2" t="n"/>
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="15" t="n"/>
+      <c r="H74" s="15">
+        <f>IF(G74="","",E74-G74)</f>
+        <v/>
+      </c>
+      <c r="I74" s="9">
+        <f>IF(AND(F74="available",G74&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H74)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
+      <c r="L74" s="9" t="n"/>
+      <c r="M74" s="9" t="n"/>
+      <c r="N74" s="9" t="n"/>
+      <c r="O74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="Q74" s="9" t="n"/>
+      <c r="R74" s="9" t="n"/>
     </row>
     <row r="75">
-      <c r="D75" s="2" t="n"/>
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="15" t="n"/>
+      <c r="H75" s="15">
+        <f>IF(G75="","",E75-G75)</f>
+        <v/>
+      </c>
+      <c r="I75" s="9">
+        <f>IF(AND(F75="available",G75&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H75)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="9" t="n"/>
+      <c r="N75" s="9" t="n"/>
+      <c r="O75" s="9" t="n"/>
+      <c r="P75" s="9" t="n"/>
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="9" t="n"/>
     </row>
     <row r="76">
-      <c r="D76" s="2" t="n"/>
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15">
+        <f>IF(G76="","",E76-G76)</f>
+        <v/>
+      </c>
+      <c r="I76" s="9">
+        <f>IF(AND(F76="available",G76&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H76)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
+      <c r="L76" s="9" t="n"/>
+      <c r="M76" s="9" t="n"/>
+      <c r="N76" s="9" t="n"/>
+      <c r="O76" s="9" t="n"/>
+      <c r="P76" s="9" t="n"/>
+      <c r="Q76" s="9" t="n"/>
+      <c r="R76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="2" t="n"/>
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="15" t="n"/>
+      <c r="H77" s="15">
+        <f>IF(G77="","",E77-G77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="9">
+        <f>IF(AND(F77="available",G77&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H77)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="9" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="2" t="n"/>
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="15" t="n"/>
+      <c r="H78" s="15">
+        <f>IF(G78="","",E78-G78)</f>
+        <v/>
+      </c>
+      <c r="I78" s="9">
+        <f>IF(AND(F78="available",G78&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H78)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="9" t="n"/>
+      <c r="L78" s="9" t="n"/>
+      <c r="M78" s="9" t="n"/>
+      <c r="N78" s="9" t="n"/>
+      <c r="O78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="Q78" s="9" t="n"/>
+      <c r="R78" s="9" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="2" t="n"/>
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="15" t="n"/>
+      <c r="H79" s="15">
+        <f>IF(G79="","",E79-G79)</f>
+        <v/>
+      </c>
+      <c r="I79" s="9">
+        <f>IF(AND(F79="available",G79&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H79)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J79" s="9" t="n"/>
+      <c r="K79" s="9" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="9" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="2" t="n"/>
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="15" t="n"/>
+      <c r="H80" s="15">
+        <f>IF(G80="","",E80-G80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="9">
+        <f>IF(AND(F80="available",G80&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H80)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="9" t="n"/>
+      <c r="L80" s="9" t="n"/>
+      <c r="M80" s="9" t="n"/>
+      <c r="N80" s="9" t="n"/>
+      <c r="O80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="Q80" s="9" t="n"/>
+      <c r="R80" s="9" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="2" t="n"/>
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="15" t="n"/>
+      <c r="H81" s="15">
+        <f>IF(G81="","",E81-G81)</f>
+        <v/>
+      </c>
+      <c r="I81" s="9">
+        <f>IF(AND(F81="available",G81&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H81)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
+      <c r="N81" s="9" t="n"/>
+      <c r="O81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="9" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="2" t="n"/>
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="15" t="n"/>
+      <c r="H82" s="15">
+        <f>IF(G82="","",E82-G82)</f>
+        <v/>
+      </c>
+      <c r="I82" s="9">
+        <f>IF(AND(F82="available",G82&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H82)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J82" s="9" t="n"/>
+      <c r="K82" s="9" t="n"/>
+      <c r="L82" s="9" t="n"/>
+      <c r="M82" s="9" t="n"/>
+      <c r="N82" s="9" t="n"/>
+      <c r="O82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="9" t="n"/>
+      <c r="R82" s="9" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="2" t="n"/>
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="15" t="n"/>
+      <c r="H83" s="15">
+        <f>IF(G83="","",E83-G83)</f>
+        <v/>
+      </c>
+      <c r="I83" s="9">
+        <f>IF(AND(F83="available",G83&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H83)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J83" s="9" t="n"/>
+      <c r="K83" s="9" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
+      <c r="O83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="9" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="2" t="n"/>
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="15" t="n"/>
+      <c r="H84" s="15">
+        <f>IF(G84="","",E84-G84)</f>
+        <v/>
+      </c>
+      <c r="I84" s="9">
+        <f>IF(AND(F84="available",G84&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H84)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+      <c r="L84" s="9" t="n"/>
+      <c r="M84" s="9" t="n"/>
+      <c r="N84" s="9" t="n"/>
+      <c r="O84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="9" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="2" t="n"/>
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="15" t="n"/>
+      <c r="H85" s="15">
+        <f>IF(G85="","",E85-G85)</f>
+        <v/>
+      </c>
+      <c r="I85" s="9">
+        <f>IF(AND(F85="available",G85&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H85)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
+      <c r="O85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="2" t="n"/>
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="15" t="n"/>
+      <c r="H86" s="15">
+        <f>IF(G86="","",E86-G86)</f>
+        <v/>
+      </c>
+      <c r="I86" s="9">
+        <f>IF(AND(F86="available",G86&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H86)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J86" s="9" t="n"/>
+      <c r="K86" s="9" t="n"/>
+      <c r="L86" s="9" t="n"/>
+      <c r="M86" s="9" t="n"/>
+      <c r="N86" s="9" t="n"/>
+      <c r="O86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="9" t="n"/>
+      <c r="R86" s="9" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="2" t="n"/>
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="15" t="n"/>
+      <c r="H87" s="15">
+        <f>IF(G87="","",E87-G87)</f>
+        <v/>
+      </c>
+      <c r="I87" s="9">
+        <f>IF(AND(F87="available",G87&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H87)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J87" s="9" t="n"/>
+      <c r="K87" s="9" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="N87" s="9" t="n"/>
+      <c r="O87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="9" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="2" t="n"/>
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="15" t="n"/>
+      <c r="H88" s="15">
+        <f>IF(G88="","",E88-G88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="9">
+        <f>IF(AND(F88="available",G88&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H88)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
+      <c r="L88" s="9" t="n"/>
+      <c r="M88" s="9" t="n"/>
+      <c r="N88" s="9" t="n"/>
+      <c r="O88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
+      <c r="Q88" s="9" t="n"/>
+      <c r="R88" s="9" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="2" t="n"/>
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="15" t="n"/>
+      <c r="H89" s="15">
+        <f>IF(G89="","",E89-G89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="9">
+        <f>IF(AND(F89="available",G89&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H89)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J89" s="9" t="n"/>
+      <c r="K89" s="9" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
+      <c r="N89" s="9" t="n"/>
+      <c r="O89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="9" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="2" t="n"/>
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="15" t="n"/>
+      <c r="H90" s="15">
+        <f>IF(G90="","",E90-G90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="9">
+        <f>IF(AND(F90="available",G90&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H90)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
+      <c r="L90" s="9" t="n"/>
+      <c r="M90" s="9" t="n"/>
+      <c r="N90" s="9" t="n"/>
+      <c r="O90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="Q90" s="9" t="n"/>
+      <c r="R90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="2" t="n"/>
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="15" t="n"/>
+      <c r="H91" s="15">
+        <f>IF(G91="","",E91-G91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="9">
+        <f>IF(AND(F91="available",G91&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H91)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
+      <c r="N91" s="9" t="n"/>
+      <c r="O91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="9" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="2" t="n"/>
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15">
+        <f>IF(G92="","",E92-G92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="9">
+        <f>IF(AND(F92="available",G92&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H92)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J92" s="9" t="n"/>
+      <c r="K92" s="9" t="n"/>
+      <c r="L92" s="9" t="n"/>
+      <c r="M92" s="9" t="n"/>
+      <c r="N92" s="9" t="n"/>
+      <c r="O92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
+      <c r="Q92" s="9" t="n"/>
+      <c r="R92" s="9" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="2" t="n"/>
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="15" t="n"/>
+      <c r="H93" s="15">
+        <f>IF(G93="","",E93-G93)</f>
+        <v/>
+      </c>
+      <c r="I93" s="9">
+        <f>IF(AND(F93="available",G93&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H93)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="9" t="n"/>
+      <c r="N93" s="9" t="n"/>
+      <c r="O93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="9" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="2" t="n"/>
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="15" t="n"/>
+      <c r="H94" s="15">
+        <f>IF(G94="","",E94-G94)</f>
+        <v/>
+      </c>
+      <c r="I94" s="9">
+        <f>IF(AND(F94="available",G94&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H94)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+      <c r="L94" s="9" t="n"/>
+      <c r="M94" s="9" t="n"/>
+      <c r="N94" s="9" t="n"/>
+      <c r="O94" s="9" t="n"/>
+      <c r="P94" s="9" t="n"/>
+      <c r="Q94" s="9" t="n"/>
+      <c r="R94" s="9" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="2" t="n"/>
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="15" t="n"/>
+      <c r="H95" s="15">
+        <f>IF(G95="","",E95-G95)</f>
+        <v/>
+      </c>
+      <c r="I95" s="9">
+        <f>IF(AND(F95="available",G95&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H95)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="N95" s="9" t="n"/>
+      <c r="O95" s="9" t="n"/>
+      <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="9" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="2" t="n"/>
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="15" t="n"/>
+      <c r="H96" s="15">
+        <f>IF(G96="","",E96-G96)</f>
+        <v/>
+      </c>
+      <c r="I96" s="9">
+        <f>IF(AND(F96="available",G96&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H96)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+      <c r="L96" s="9" t="n"/>
+      <c r="M96" s="9" t="n"/>
+      <c r="N96" s="9" t="n"/>
+      <c r="O96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="9" t="n"/>
+      <c r="R96" s="9" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="2" t="n"/>
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="15" t="n"/>
+      <c r="H97" s="15">
+        <f>IF(G97="","",E97-G97)</f>
+        <v/>
+      </c>
+      <c r="I97" s="9">
+        <f>IF(AND(F97="available",G97&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H97)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
+      <c r="O97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="9" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="2" t="n"/>
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="15" t="n"/>
+      <c r="H98" s="15">
+        <f>IF(G98="","",E98-G98)</f>
+        <v/>
+      </c>
+      <c r="I98" s="9">
+        <f>IF(AND(F98="available",G98&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H98)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+      <c r="L98" s="9" t="n"/>
+      <c r="M98" s="9" t="n"/>
+      <c r="N98" s="9" t="n"/>
+      <c r="O98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
+      <c r="Q98" s="9" t="n"/>
+      <c r="R98" s="9" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="2" t="n"/>
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n"/>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="15" t="n"/>
+      <c r="H99" s="15">
+        <f>IF(G99="","",E99-G99)</f>
+        <v/>
+      </c>
+      <c r="I99" s="9">
+        <f>IF(AND(F99="available",G99&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H99)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
+      <c r="O99" s="9" t="n"/>
+      <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="9" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="2" t="n"/>
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="15" t="n"/>
+      <c r="H100" s="15">
+        <f>IF(G100="","",E100-G100)</f>
+        <v/>
+      </c>
+      <c r="I100" s="9">
+        <f>IF(AND(F100="available",G100&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H100)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="9" t="n"/>
+      <c r="M100" s="9" t="n"/>
+      <c r="N100" s="9" t="n"/>
+      <c r="O100" s="9" t="n"/>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="9" t="n"/>
+      <c r="R100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="2" t="n"/>
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="15" t="n"/>
+      <c r="H101" s="15">
+        <f>IF(G101="","",E101-G101)</f>
+        <v/>
+      </c>
+      <c r="I101" s="9">
+        <f>IF(AND(F101="available",G101&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H101)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
+      <c r="N101" s="9" t="n"/>
+      <c r="O101" s="9" t="n"/>
+      <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="9" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="2" t="n"/>
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="15" t="n"/>
+      <c r="H102" s="15">
+        <f>IF(G102="","",E102-G102)</f>
+        <v/>
+      </c>
+      <c r="I102" s="9">
+        <f>IF(AND(F102="available",G102&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H102)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="L102" s="9" t="n"/>
+      <c r="M102" s="9" t="n"/>
+      <c r="N102" s="9" t="n"/>
+      <c r="O102" s="9" t="n"/>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="9" t="n"/>
+      <c r="R102" s="9" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="2" t="n"/>
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="15" t="n"/>
+      <c r="H103" s="15">
+        <f>IF(G103="","",E103-G103)</f>
+        <v/>
+      </c>
+      <c r="I103" s="9">
+        <f>IF(AND(F103="available",G103&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H103)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
+      <c r="N103" s="9" t="n"/>
+      <c r="O103" s="9" t="n"/>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="9" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="2" t="n"/>
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="15" t="n"/>
+      <c r="H104" s="15">
+        <f>IF(G104="","",E104-G104)</f>
+        <v/>
+      </c>
+      <c r="I104" s="9">
+        <f>IF(AND(F104="available",G104&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H104)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="L104" s="9" t="n"/>
+      <c r="M104" s="9" t="n"/>
+      <c r="N104" s="9" t="n"/>
+      <c r="O104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="Q104" s="9" t="n"/>
+      <c r="R104" s="9" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="2" t="n"/>
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="15" t="n"/>
+      <c r="H105" s="15">
+        <f>IF(G105="","",E105-G105)</f>
+        <v/>
+      </c>
+      <c r="I105" s="9">
+        <f>IF(AND(F105="available",G105&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H105)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="9" t="n"/>
+      <c r="O105" s="9" t="n"/>
+      <c r="P105" s="9" t="n"/>
+      <c r="Q105" s="9" t="n"/>
+      <c r="R105" s="9" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="2" t="n"/>
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="15" t="n"/>
+      <c r="H106" s="15">
+        <f>IF(G106="","",E106-G106)</f>
+        <v/>
+      </c>
+      <c r="I106" s="9">
+        <f>IF(AND(F106="available",G106&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H106)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="L106" s="9" t="n"/>
+      <c r="M106" s="9" t="n"/>
+      <c r="N106" s="9" t="n"/>
+      <c r="O106" s="9" t="n"/>
+      <c r="P106" s="9" t="n"/>
+      <c r="Q106" s="9" t="n"/>
+      <c r="R106" s="9" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="2" t="n"/>
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="15" t="n"/>
+      <c r="H107" s="15">
+        <f>IF(G107="","",E107-G107)</f>
+        <v/>
+      </c>
+      <c r="I107" s="9">
+        <f>IF(AND(F107="available",G107&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H107)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="9" t="n"/>
+      <c r="P107" s="9" t="n"/>
+      <c r="Q107" s="9" t="n"/>
+      <c r="R107" s="9" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="2" t="n"/>
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="15" t="n"/>
+      <c r="H108" s="15">
+        <f>IF(G108="","",E108-G108)</f>
+        <v/>
+      </c>
+      <c r="I108" s="9">
+        <f>IF(AND(F108="available",G108&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H108)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
+      <c r="L108" s="9" t="n"/>
+      <c r="M108" s="9" t="n"/>
+      <c r="N108" s="9" t="n"/>
+      <c r="O108" s="9" t="n"/>
+      <c r="P108" s="9" t="n"/>
+      <c r="Q108" s="9" t="n"/>
+      <c r="R108" s="9" t="n"/>
     </row>
     <row r="109">
-      <c r="D109" s="2" t="n"/>
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="15" t="n"/>
+      <c r="H109" s="15">
+        <f>IF(G109="","",E109-G109)</f>
+        <v/>
+      </c>
+      <c r="I109" s="9">
+        <f>IF(AND(F109="available",G109&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H109)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
+      <c r="L109" s="9" t="n"/>
+      <c r="M109" s="9" t="n"/>
+      <c r="N109" s="9" t="n"/>
+      <c r="O109" s="9" t="n"/>
+      <c r="P109" s="9" t="n"/>
+      <c r="Q109" s="9" t="n"/>
+      <c r="R109" s="9" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="2" t="n"/>
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="15" t="n"/>
+      <c r="H110" s="15">
+        <f>IF(G110="","",E110-G110)</f>
+        <v/>
+      </c>
+      <c r="I110" s="9">
+        <f>IF(AND(F110="available",G110&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H110)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J110" s="9" t="n"/>
+      <c r="K110" s="9" t="n"/>
+      <c r="L110" s="9" t="n"/>
+      <c r="M110" s="9" t="n"/>
+      <c r="N110" s="9" t="n"/>
+      <c r="O110" s="9" t="n"/>
+      <c r="P110" s="9" t="n"/>
+      <c r="Q110" s="9" t="n"/>
+      <c r="R110" s="9" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" s="2" t="n"/>
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="9" t="n"/>
+      <c r="C111" s="9" t="n"/>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="15" t="n"/>
+      <c r="H111" s="15">
+        <f>IF(G111="","",E111-G111)</f>
+        <v/>
+      </c>
+      <c r="I111" s="9">
+        <f>IF(AND(F111="available",G111&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H111)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+      <c r="L111" s="9" t="n"/>
+      <c r="M111" s="9" t="n"/>
+      <c r="N111" s="9" t="n"/>
+      <c r="O111" s="9" t="n"/>
+      <c r="P111" s="9" t="n"/>
+      <c r="Q111" s="9" t="n"/>
+      <c r="R111" s="9" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="2" t="n"/>
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="15" t="n"/>
+      <c r="H112" s="15">
+        <f>IF(G112="","",E112-G112)</f>
+        <v/>
+      </c>
+      <c r="I112" s="9">
+        <f>IF(AND(F112="available",G112&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H112)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+      <c r="L112" s="9" t="n"/>
+      <c r="M112" s="9" t="n"/>
+      <c r="N112" s="9" t="n"/>
+      <c r="O112" s="9" t="n"/>
+      <c r="P112" s="9" t="n"/>
+      <c r="Q112" s="9" t="n"/>
+      <c r="R112" s="9" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="2" t="n"/>
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="15" t="n"/>
+      <c r="H113" s="15">
+        <f>IF(G113="","",E113-G113)</f>
+        <v/>
+      </c>
+      <c r="I113" s="9">
+        <f>IF(AND(F113="available",G113&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H113)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
+      <c r="L113" s="9" t="n"/>
+      <c r="M113" s="9" t="n"/>
+      <c r="N113" s="9" t="n"/>
+      <c r="O113" s="9" t="n"/>
+      <c r="P113" s="9" t="n"/>
+      <c r="Q113" s="9" t="n"/>
+      <c r="R113" s="9" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="2" t="n"/>
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="15" t="n"/>
+      <c r="H114" s="15">
+        <f>IF(G114="","",E114-G114)</f>
+        <v/>
+      </c>
+      <c r="I114" s="9">
+        <f>IF(AND(F114="available",G114&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H114)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
+      <c r="L114" s="9" t="n"/>
+      <c r="M114" s="9" t="n"/>
+      <c r="N114" s="9" t="n"/>
+      <c r="O114" s="9" t="n"/>
+      <c r="P114" s="9" t="n"/>
+      <c r="Q114" s="9" t="n"/>
+      <c r="R114" s="9" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="2" t="n"/>
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="15" t="n"/>
+      <c r="H115" s="15">
+        <f>IF(G115="","",E115-G115)</f>
+        <v/>
+      </c>
+      <c r="I115" s="9">
+        <f>IF(AND(F115="available",G115&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H115)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J115" s="9" t="n"/>
+      <c r="K115" s="9" t="n"/>
+      <c r="L115" s="9" t="n"/>
+      <c r="M115" s="9" t="n"/>
+      <c r="N115" s="9" t="n"/>
+      <c r="O115" s="9" t="n"/>
+      <c r="P115" s="9" t="n"/>
+      <c r="Q115" s="9" t="n"/>
+      <c r="R115" s="9" t="n"/>
     </row>
     <row r="116">
-      <c r="D116" s="2" t="n"/>
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="15" t="n"/>
+      <c r="H116" s="15">
+        <f>IF(G116="","",E116-G116)</f>
+        <v/>
+      </c>
+      <c r="I116" s="9">
+        <f>IF(AND(F116="available",G116&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H116)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
+      <c r="L116" s="9" t="n"/>
+      <c r="M116" s="9" t="n"/>
+      <c r="N116" s="9" t="n"/>
+      <c r="O116" s="9" t="n"/>
+      <c r="P116" s="9" t="n"/>
+      <c r="Q116" s="9" t="n"/>
+      <c r="R116" s="9" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="2" t="n"/>
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="15" t="n"/>
+      <c r="H117" s="15">
+        <f>IF(G117="","",E117-G117)</f>
+        <v/>
+      </c>
+      <c r="I117" s="9">
+        <f>IF(AND(F117="available",G117&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H117)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+      <c r="L117" s="9" t="n"/>
+      <c r="M117" s="9" t="n"/>
+      <c r="N117" s="9" t="n"/>
+      <c r="O117" s="9" t="n"/>
+      <c r="P117" s="9" t="n"/>
+      <c r="Q117" s="9" t="n"/>
+      <c r="R117" s="9" t="n"/>
     </row>
     <row r="118">
-      <c r="D118" s="2" t="n"/>
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="15" t="n"/>
+      <c r="H118" s="15">
+        <f>IF(G118="","",E118-G118)</f>
+        <v/>
+      </c>
+      <c r="I118" s="9">
+        <f>IF(AND(F118="available",G118&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H118)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J118" s="9" t="n"/>
+      <c r="K118" s="9" t="n"/>
+      <c r="L118" s="9" t="n"/>
+      <c r="M118" s="9" t="n"/>
+      <c r="N118" s="9" t="n"/>
+      <c r="O118" s="9" t="n"/>
+      <c r="P118" s="9" t="n"/>
+      <c r="Q118" s="9" t="n"/>
+      <c r="R118" s="9" t="n"/>
     </row>
     <row r="119">
-      <c r="D119" s="2" t="n"/>
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="9" t="n"/>
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="15" t="n"/>
+      <c r="H119" s="15">
+        <f>IF(G119="","",E119-G119)</f>
+        <v/>
+      </c>
+      <c r="I119" s="9">
+        <f>IF(AND(F119="available",G119&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H119)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J119" s="9" t="n"/>
+      <c r="K119" s="9" t="n"/>
+      <c r="L119" s="9" t="n"/>
+      <c r="M119" s="9" t="n"/>
+      <c r="N119" s="9" t="n"/>
+      <c r="O119" s="9" t="n"/>
+      <c r="P119" s="9" t="n"/>
+      <c r="Q119" s="9" t="n"/>
+      <c r="R119" s="9" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="2" t="n"/>
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="9" t="n"/>
+      <c r="G120" s="15" t="n"/>
+      <c r="H120" s="15">
+        <f>IF(G120="","",E120-G120)</f>
+        <v/>
+      </c>
+      <c r="I120" s="9">
+        <f>IF(AND(F120="available",G120&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H120)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
+      <c r="L120" s="9" t="n"/>
+      <c r="M120" s="9" t="n"/>
+      <c r="N120" s="9" t="n"/>
+      <c r="O120" s="9" t="n"/>
+      <c r="P120" s="9" t="n"/>
+      <c r="Q120" s="9" t="n"/>
+      <c r="R120" s="9" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="2" t="n"/>
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="9" t="n"/>
+      <c r="G121" s="15" t="n"/>
+      <c r="H121" s="15">
+        <f>IF(G121="","",E121-G121)</f>
+        <v/>
+      </c>
+      <c r="I121" s="9">
+        <f>IF(AND(F121="available",G121&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H121)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J121" s="9" t="n"/>
+      <c r="K121" s="9" t="n"/>
+      <c r="L121" s="9" t="n"/>
+      <c r="M121" s="9" t="n"/>
+      <c r="N121" s="9" t="n"/>
+      <c r="O121" s="9" t="n"/>
+      <c r="P121" s="9" t="n"/>
+      <c r="Q121" s="9" t="n"/>
+      <c r="R121" s="9" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="2" t="n"/>
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="15" t="n"/>
+      <c r="H122" s="15">
+        <f>IF(G122="","",E122-G122)</f>
+        <v/>
+      </c>
+      <c r="I122" s="9">
+        <f>IF(AND(F122="available",G122&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H122)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
+      <c r="L122" s="9" t="n"/>
+      <c r="M122" s="9" t="n"/>
+      <c r="N122" s="9" t="n"/>
+      <c r="O122" s="9" t="n"/>
+      <c r="P122" s="9" t="n"/>
+      <c r="Q122" s="9" t="n"/>
+      <c r="R122" s="9" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="2" t="n"/>
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="15" t="n"/>
+      <c r="H123" s="15">
+        <f>IF(G123="","",E123-G123)</f>
+        <v/>
+      </c>
+      <c r="I123" s="9">
+        <f>IF(AND(F123="available",G123&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H123)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J123" s="9" t="n"/>
+      <c r="K123" s="9" t="n"/>
+      <c r="L123" s="9" t="n"/>
+      <c r="M123" s="9" t="n"/>
+      <c r="N123" s="9" t="n"/>
+      <c r="O123" s="9" t="n"/>
+      <c r="P123" s="9" t="n"/>
+      <c r="Q123" s="9" t="n"/>
+      <c r="R123" s="9" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="2" t="n"/>
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="15" t="n"/>
+      <c r="H124" s="15">
+        <f>IF(G124="","",E124-G124)</f>
+        <v/>
+      </c>
+      <c r="I124" s="9">
+        <f>IF(AND(F124="available",G124&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H124)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J124" s="9" t="n"/>
+      <c r="K124" s="9" t="n"/>
+      <c r="L124" s="9" t="n"/>
+      <c r="M124" s="9" t="n"/>
+      <c r="N124" s="9" t="n"/>
+      <c r="O124" s="9" t="n"/>
+      <c r="P124" s="9" t="n"/>
+      <c r="Q124" s="9" t="n"/>
+      <c r="R124" s="9" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="2" t="n"/>
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="9" t="n"/>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="15" t="n"/>
+      <c r="H125" s="15">
+        <f>IF(G125="","",E125-G125)</f>
+        <v/>
+      </c>
+      <c r="I125" s="9">
+        <f>IF(AND(F125="available",G125&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H125)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
+      <c r="L125" s="9" t="n"/>
+      <c r="M125" s="9" t="n"/>
+      <c r="N125" s="9" t="n"/>
+      <c r="O125" s="9" t="n"/>
+      <c r="P125" s="9" t="n"/>
+      <c r="Q125" s="9" t="n"/>
+      <c r="R125" s="9" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="2" t="n"/>
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="15" t="n"/>
+      <c r="H126" s="15">
+        <f>IF(G126="","",E126-G126)</f>
+        <v/>
+      </c>
+      <c r="I126" s="9">
+        <f>IF(AND(F126="available",G126&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H126)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J126" s="9" t="n"/>
+      <c r="K126" s="9" t="n"/>
+      <c r="L126" s="9" t="n"/>
+      <c r="M126" s="9" t="n"/>
+      <c r="N126" s="9" t="n"/>
+      <c r="O126" s="9" t="n"/>
+      <c r="P126" s="9" t="n"/>
+      <c r="Q126" s="9" t="n"/>
+      <c r="R126" s="9" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="2" t="n"/>
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="15" t="n"/>
+      <c r="H127" s="15">
+        <f>IF(G127="","",E127-G127)</f>
+        <v/>
+      </c>
+      <c r="I127" s="9">
+        <f>IF(AND(F127="available",G127&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H127)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J127" s="9" t="n"/>
+      <c r="K127" s="9" t="n"/>
+      <c r="L127" s="9" t="n"/>
+      <c r="M127" s="9" t="n"/>
+      <c r="N127" s="9" t="n"/>
+      <c r="O127" s="9" t="n"/>
+      <c r="P127" s="9" t="n"/>
+      <c r="Q127" s="9" t="n"/>
+      <c r="R127" s="9" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="2" t="n"/>
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="15" t="n"/>
+      <c r="H128" s="15">
+        <f>IF(G128="","",E128-G128)</f>
+        <v/>
+      </c>
+      <c r="I128" s="9">
+        <f>IF(AND(F128="available",G128&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H128)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J128" s="9" t="n"/>
+      <c r="K128" s="9" t="n"/>
+      <c r="L128" s="9" t="n"/>
+      <c r="M128" s="9" t="n"/>
+      <c r="N128" s="9" t="n"/>
+      <c r="O128" s="9" t="n"/>
+      <c r="P128" s="9" t="n"/>
+      <c r="Q128" s="9" t="n"/>
+      <c r="R128" s="9" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="2" t="n"/>
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="15" t="n"/>
+      <c r="H129" s="15">
+        <f>IF(G129="","",E129-G129)</f>
+        <v/>
+      </c>
+      <c r="I129" s="9">
+        <f>IF(AND(F129="available",G129&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H129)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J129" s="9" t="n"/>
+      <c r="K129" s="9" t="n"/>
+      <c r="L129" s="9" t="n"/>
+      <c r="M129" s="9" t="n"/>
+      <c r="N129" s="9" t="n"/>
+      <c r="O129" s="9" t="n"/>
+      <c r="P129" s="9" t="n"/>
+      <c r="Q129" s="9" t="n"/>
+      <c r="R129" s="9" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="2" t="n"/>
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="9" t="n"/>
+      <c r="G130" s="15" t="n"/>
+      <c r="H130" s="15">
+        <f>IF(G130="","",E130-G130)</f>
+        <v/>
+      </c>
+      <c r="I130" s="9">
+        <f>IF(AND(F130="available",G130&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H130)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J130" s="9" t="n"/>
+      <c r="K130" s="9" t="n"/>
+      <c r="L130" s="9" t="n"/>
+      <c r="M130" s="9" t="n"/>
+      <c r="N130" s="9" t="n"/>
+      <c r="O130" s="9" t="n"/>
+      <c r="P130" s="9" t="n"/>
+      <c r="Q130" s="9" t="n"/>
+      <c r="R130" s="9" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="2" t="n"/>
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="15" t="n"/>
+      <c r="H131" s="15">
+        <f>IF(G131="","",E131-G131)</f>
+        <v/>
+      </c>
+      <c r="I131" s="9">
+        <f>IF(AND(F131="available",G131&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H131)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J131" s="9" t="n"/>
+      <c r="K131" s="9" t="n"/>
+      <c r="L131" s="9" t="n"/>
+      <c r="M131" s="9" t="n"/>
+      <c r="N131" s="9" t="n"/>
+      <c r="O131" s="9" t="n"/>
+      <c r="P131" s="9" t="n"/>
+      <c r="Q131" s="9" t="n"/>
+      <c r="R131" s="9" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="2" t="n"/>
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="15" t="n"/>
+      <c r="H132" s="15">
+        <f>IF(G132="","",E132-G132)</f>
+        <v/>
+      </c>
+      <c r="I132" s="9">
+        <f>IF(AND(F132="available",G132&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H132)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J132" s="9" t="n"/>
+      <c r="K132" s="9" t="n"/>
+      <c r="L132" s="9" t="n"/>
+      <c r="M132" s="9" t="n"/>
+      <c r="N132" s="9" t="n"/>
+      <c r="O132" s="9" t="n"/>
+      <c r="P132" s="9" t="n"/>
+      <c r="Q132" s="9" t="n"/>
+      <c r="R132" s="9" t="n"/>
     </row>
     <row r="133">
-      <c r="D133" s="2" t="n"/>
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="9" t="n"/>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="9" t="n"/>
+      <c r="F133" s="9" t="n"/>
+      <c r="G133" s="15" t="n"/>
+      <c r="H133" s="15">
+        <f>IF(G133="","",E133-G133)</f>
+        <v/>
+      </c>
+      <c r="I133" s="9">
+        <f>IF(AND(F133="available",G133&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H133)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J133" s="9" t="n"/>
+      <c r="K133" s="9" t="n"/>
+      <c r="L133" s="9" t="n"/>
+      <c r="M133" s="9" t="n"/>
+      <c r="N133" s="9" t="n"/>
+      <c r="O133" s="9" t="n"/>
+      <c r="P133" s="9" t="n"/>
+      <c r="Q133" s="9" t="n"/>
+      <c r="R133" s="9" t="n"/>
     </row>
     <row r="134">
-      <c r="D134" s="2" t="n"/>
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="9" t="n"/>
+      <c r="G134" s="15" t="n"/>
+      <c r="H134" s="15">
+        <f>IF(G134="","",E134-G134)</f>
+        <v/>
+      </c>
+      <c r="I134" s="9">
+        <f>IF(AND(F134="available",G134&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H134)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J134" s="9" t="n"/>
+      <c r="K134" s="9" t="n"/>
+      <c r="L134" s="9" t="n"/>
+      <c r="M134" s="9" t="n"/>
+      <c r="N134" s="9" t="n"/>
+      <c r="O134" s="9" t="n"/>
+      <c r="P134" s="9" t="n"/>
+      <c r="Q134" s="9" t="n"/>
+      <c r="R134" s="9" t="n"/>
     </row>
     <row r="135">
-      <c r="D135" s="2" t="n"/>
+      <c r="A135" s="9" t="n"/>
+      <c r="B135" s="9" t="n"/>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="9" t="n"/>
+      <c r="G135" s="15" t="n"/>
+      <c r="H135" s="15">
+        <f>IF(G135="","",E135-G135)</f>
+        <v/>
+      </c>
+      <c r="I135" s="9">
+        <f>IF(AND(F135="available",G135&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H135)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J135" s="9" t="n"/>
+      <c r="K135" s="9" t="n"/>
+      <c r="L135" s="9" t="n"/>
+      <c r="M135" s="9" t="n"/>
+      <c r="N135" s="9" t="n"/>
+      <c r="O135" s="9" t="n"/>
+      <c r="P135" s="9" t="n"/>
+      <c r="Q135" s="9" t="n"/>
+      <c r="R135" s="9" t="n"/>
     </row>
     <row r="136">
-      <c r="D136" s="2" t="n"/>
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="9" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="9" t="n"/>
+      <c r="G136" s="15" t="n"/>
+      <c r="H136" s="15">
+        <f>IF(G136="","",E136-G136)</f>
+        <v/>
+      </c>
+      <c r="I136" s="9">
+        <f>IF(AND(F136="available",G136&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H136)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J136" s="9" t="n"/>
+      <c r="K136" s="9" t="n"/>
+      <c r="L136" s="9" t="n"/>
+      <c r="M136" s="9" t="n"/>
+      <c r="N136" s="9" t="n"/>
+      <c r="O136" s="9" t="n"/>
+      <c r="P136" s="9" t="n"/>
+      <c r="Q136" s="9" t="n"/>
+      <c r="R136" s="9" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="2" t="n"/>
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="9" t="n"/>
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="9" t="n"/>
+      <c r="G137" s="15" t="n"/>
+      <c r="H137" s="15">
+        <f>IF(G137="","",E137-G137)</f>
+        <v/>
+      </c>
+      <c r="I137" s="9">
+        <f>IF(AND(F137="available",G137&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H137)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
+      <c r="L137" s="9" t="n"/>
+      <c r="M137" s="9" t="n"/>
+      <c r="N137" s="9" t="n"/>
+      <c r="O137" s="9" t="n"/>
+      <c r="P137" s="9" t="n"/>
+      <c r="Q137" s="9" t="n"/>
+      <c r="R137" s="9" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="2" t="n"/>
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="9" t="n"/>
+      <c r="G138" s="15" t="n"/>
+      <c r="H138" s="15">
+        <f>IF(G138="","",E138-G138)</f>
+        <v/>
+      </c>
+      <c r="I138" s="9">
+        <f>IF(AND(F138="available",G138&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H138)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J138" s="9" t="n"/>
+      <c r="K138" s="9" t="n"/>
+      <c r="L138" s="9" t="n"/>
+      <c r="M138" s="9" t="n"/>
+      <c r="N138" s="9" t="n"/>
+      <c r="O138" s="9" t="n"/>
+      <c r="P138" s="9" t="n"/>
+      <c r="Q138" s="9" t="n"/>
+      <c r="R138" s="9" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="2" t="n"/>
+      <c r="A139" s="9" t="n"/>
+      <c r="B139" s="9" t="n"/>
+      <c r="C139" s="9" t="n"/>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="9" t="n"/>
+      <c r="F139" s="9" t="n"/>
+      <c r="G139" s="15" t="n"/>
+      <c r="H139" s="15">
+        <f>IF(G139="","",E139-G139)</f>
+        <v/>
+      </c>
+      <c r="I139" s="9">
+        <f>IF(AND(F139="available",G139&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H139)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J139" s="9" t="n"/>
+      <c r="K139" s="9" t="n"/>
+      <c r="L139" s="9" t="n"/>
+      <c r="M139" s="9" t="n"/>
+      <c r="N139" s="9" t="n"/>
+      <c r="O139" s="9" t="n"/>
+      <c r="P139" s="9" t="n"/>
+      <c r="Q139" s="9" t="n"/>
+      <c r="R139" s="9" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="2" t="n"/>
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="15" t="n"/>
+      <c r="H140" s="15">
+        <f>IF(G140="","",E140-G140)</f>
+        <v/>
+      </c>
+      <c r="I140" s="9">
+        <f>IF(AND(F140="available",G140&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H140)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="9" t="n"/>
+      <c r="L140" s="9" t="n"/>
+      <c r="M140" s="9" t="n"/>
+      <c r="N140" s="9" t="n"/>
+      <c r="O140" s="9" t="n"/>
+      <c r="P140" s="9" t="n"/>
+      <c r="Q140" s="9" t="n"/>
+      <c r="R140" s="9" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="2" t="n"/>
+      <c r="A141" s="9" t="n"/>
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="9" t="n"/>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="9" t="n"/>
+      <c r="F141" s="9" t="n"/>
+      <c r="G141" s="15" t="n"/>
+      <c r="H141" s="15">
+        <f>IF(G141="","",E141-G141)</f>
+        <v/>
+      </c>
+      <c r="I141" s="9">
+        <f>IF(AND(F141="available",G141&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H141)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J141" s="9" t="n"/>
+      <c r="K141" s="9" t="n"/>
+      <c r="L141" s="9" t="n"/>
+      <c r="M141" s="9" t="n"/>
+      <c r="N141" s="9" t="n"/>
+      <c r="O141" s="9" t="n"/>
+      <c r="P141" s="9" t="n"/>
+      <c r="Q141" s="9" t="n"/>
+      <c r="R141" s="9" t="n"/>
     </row>
     <row r="142">
-      <c r="D142" s="2" t="n"/>
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="15" t="n"/>
+      <c r="H142" s="15">
+        <f>IF(G142="","",E142-G142)</f>
+        <v/>
+      </c>
+      <c r="I142" s="9">
+        <f>IF(AND(F142="available",G142&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H142)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J142" s="9" t="n"/>
+      <c r="K142" s="9" t="n"/>
+      <c r="L142" s="9" t="n"/>
+      <c r="M142" s="9" t="n"/>
+      <c r="N142" s="9" t="n"/>
+      <c r="O142" s="9" t="n"/>
+      <c r="P142" s="9" t="n"/>
+      <c r="Q142" s="9" t="n"/>
+      <c r="R142" s="9" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="2" t="n"/>
+      <c r="A143" s="9" t="n"/>
+      <c r="B143" s="9" t="n"/>
+      <c r="C143" s="9" t="n"/>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="9" t="n"/>
+      <c r="F143" s="9" t="n"/>
+      <c r="G143" s="15" t="n"/>
+      <c r="H143" s="15">
+        <f>IF(G143="","",E143-G143)</f>
+        <v/>
+      </c>
+      <c r="I143" s="9">
+        <f>IF(AND(F143="available",G143&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H143)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J143" s="9" t="n"/>
+      <c r="K143" s="9" t="n"/>
+      <c r="L143" s="9" t="n"/>
+      <c r="M143" s="9" t="n"/>
+      <c r="N143" s="9" t="n"/>
+      <c r="O143" s="9" t="n"/>
+      <c r="P143" s="9" t="n"/>
+      <c r="Q143" s="9" t="n"/>
+      <c r="R143" s="9" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="2" t="n"/>
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="15" t="n"/>
+      <c r="H144" s="15">
+        <f>IF(G144="","",E144-G144)</f>
+        <v/>
+      </c>
+      <c r="I144" s="9">
+        <f>IF(AND(F144="available",G144&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H144)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
+      <c r="L144" s="9" t="n"/>
+      <c r="M144" s="9" t="n"/>
+      <c r="N144" s="9" t="n"/>
+      <c r="O144" s="9" t="n"/>
+      <c r="P144" s="9" t="n"/>
+      <c r="Q144" s="9" t="n"/>
+      <c r="R144" s="9" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="2" t="n"/>
+      <c r="A145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="9" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="9" t="n"/>
+      <c r="F145" s="9" t="n"/>
+      <c r="G145" s="15" t="n"/>
+      <c r="H145" s="15">
+        <f>IF(G145="","",E145-G145)</f>
+        <v/>
+      </c>
+      <c r="I145" s="9">
+        <f>IF(AND(F145="available",G145&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H145)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J145" s="9" t="n"/>
+      <c r="K145" s="9" t="n"/>
+      <c r="L145" s="9" t="n"/>
+      <c r="M145" s="9" t="n"/>
+      <c r="N145" s="9" t="n"/>
+      <c r="O145" s="9" t="n"/>
+      <c r="P145" s="9" t="n"/>
+      <c r="Q145" s="9" t="n"/>
+      <c r="R145" s="9" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="2" t="n"/>
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="15" t="n"/>
+      <c r="H146" s="15">
+        <f>IF(G146="","",E146-G146)</f>
+        <v/>
+      </c>
+      <c r="I146" s="9">
+        <f>IF(AND(F146="available",G146&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H146)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J146" s="9" t="n"/>
+      <c r="K146" s="9" t="n"/>
+      <c r="L146" s="9" t="n"/>
+      <c r="M146" s="9" t="n"/>
+      <c r="N146" s="9" t="n"/>
+      <c r="O146" s="9" t="n"/>
+      <c r="P146" s="9" t="n"/>
+      <c r="Q146" s="9" t="n"/>
+      <c r="R146" s="9" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="2" t="n"/>
+      <c r="A147" s="9" t="n"/>
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="15" t="n"/>
+      <c r="H147" s="15">
+        <f>IF(G147="","",E147-G147)</f>
+        <v/>
+      </c>
+      <c r="I147" s="9">
+        <f>IF(AND(F147="available",G147&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H147)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J147" s="9" t="n"/>
+      <c r="K147" s="9" t="n"/>
+      <c r="L147" s="9" t="n"/>
+      <c r="M147" s="9" t="n"/>
+      <c r="N147" s="9" t="n"/>
+      <c r="O147" s="9" t="n"/>
+      <c r="P147" s="9" t="n"/>
+      <c r="Q147" s="9" t="n"/>
+      <c r="R147" s="9" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="2" t="n"/>
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="10" t="n"/>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="9" t="n"/>
+      <c r="G148" s="15" t="n"/>
+      <c r="H148" s="15">
+        <f>IF(G148="","",E148-G148)</f>
+        <v/>
+      </c>
+      <c r="I148" s="9">
+        <f>IF(AND(F148="available",G148&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H148)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J148" s="9" t="n"/>
+      <c r="K148" s="9" t="n"/>
+      <c r="L148" s="9" t="n"/>
+      <c r="M148" s="9" t="n"/>
+      <c r="N148" s="9" t="n"/>
+      <c r="O148" s="9" t="n"/>
+      <c r="P148" s="9" t="n"/>
+      <c r="Q148" s="9" t="n"/>
+      <c r="R148" s="9" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="2" t="n"/>
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="9" t="n"/>
+      <c r="C149" s="9" t="n"/>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="9" t="n"/>
+      <c r="F149" s="9" t="n"/>
+      <c r="G149" s="15" t="n"/>
+      <c r="H149" s="15">
+        <f>IF(G149="","",E149-G149)</f>
+        <v/>
+      </c>
+      <c r="I149" s="9">
+        <f>IF(AND(F149="available",G149&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H149)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J149" s="9" t="n"/>
+      <c r="K149" s="9" t="n"/>
+      <c r="L149" s="9" t="n"/>
+      <c r="M149" s="9" t="n"/>
+      <c r="N149" s="9" t="n"/>
+      <c r="O149" s="9" t="n"/>
+      <c r="P149" s="9" t="n"/>
+      <c r="Q149" s="9" t="n"/>
+      <c r="R149" s="9" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="2" t="n"/>
+      <c r="A150" s="9" t="n"/>
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="10" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="9" t="n"/>
+      <c r="G150" s="15" t="n"/>
+      <c r="H150" s="15">
+        <f>IF(G150="","",E150-G150)</f>
+        <v/>
+      </c>
+      <c r="I150" s="9">
+        <f>IF(AND(F150="available",G150&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H150)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J150" s="9" t="n"/>
+      <c r="K150" s="9" t="n"/>
+      <c r="L150" s="9" t="n"/>
+      <c r="M150" s="9" t="n"/>
+      <c r="N150" s="9" t="n"/>
+      <c r="O150" s="9" t="n"/>
+      <c r="P150" s="9" t="n"/>
+      <c r="Q150" s="9" t="n"/>
+      <c r="R150" s="9" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="2" t="n"/>
+      <c r="A151" s="9" t="n"/>
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="9" t="n"/>
+      <c r="D151" s="10" t="n"/>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="9" t="n"/>
+      <c r="G151" s="15" t="n"/>
+      <c r="H151" s="15">
+        <f>IF(G151="","",E151-G151)</f>
+        <v/>
+      </c>
+      <c r="I151" s="9">
+        <f>IF(AND(F151="available",G151&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H151)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J151" s="9" t="n"/>
+      <c r="K151" s="9" t="n"/>
+      <c r="L151" s="9" t="n"/>
+      <c r="M151" s="9" t="n"/>
+      <c r="N151" s="9" t="n"/>
+      <c r="O151" s="9" t="n"/>
+      <c r="P151" s="9" t="n"/>
+      <c r="Q151" s="9" t="n"/>
+      <c r="R151" s="9" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="2" t="n"/>
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="10" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="15" t="n"/>
+      <c r="H152" s="15">
+        <f>IF(G152="","",E152-G152)</f>
+        <v/>
+      </c>
+      <c r="I152" s="9">
+        <f>IF(AND(F152="available",G152&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H152)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J152" s="9" t="n"/>
+      <c r="K152" s="9" t="n"/>
+      <c r="L152" s="9" t="n"/>
+      <c r="M152" s="9" t="n"/>
+      <c r="N152" s="9" t="n"/>
+      <c r="O152" s="9" t="n"/>
+      <c r="P152" s="9" t="n"/>
+      <c r="Q152" s="9" t="n"/>
+      <c r="R152" s="9" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="2" t="n"/>
+      <c r="A153" s="9" t="n"/>
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="9" t="n"/>
+      <c r="D153" s="10" t="n"/>
+      <c r="E153" s="9" t="n"/>
+      <c r="F153" s="9" t="n"/>
+      <c r="G153" s="15" t="n"/>
+      <c r="H153" s="15">
+        <f>IF(G153="","",E153-G153)</f>
+        <v/>
+      </c>
+      <c r="I153" s="9">
+        <f>IF(AND(F153="available",G153&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H153)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J153" s="9" t="n"/>
+      <c r="K153" s="9" t="n"/>
+      <c r="L153" s="9" t="n"/>
+      <c r="M153" s="9" t="n"/>
+      <c r="N153" s="9" t="n"/>
+      <c r="O153" s="9" t="n"/>
+      <c r="P153" s="9" t="n"/>
+      <c r="Q153" s="9" t="n"/>
+      <c r="R153" s="9" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="2" t="n"/>
+      <c r="A154" s="9" t="n"/>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="9" t="n"/>
+      <c r="F154" s="9" t="n"/>
+      <c r="G154" s="15" t="n"/>
+      <c r="H154" s="15">
+        <f>IF(G154="","",E154-G154)</f>
+        <v/>
+      </c>
+      <c r="I154" s="9">
+        <f>IF(AND(F154="available",G154&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H154)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J154" s="9" t="n"/>
+      <c r="K154" s="9" t="n"/>
+      <c r="L154" s="9" t="n"/>
+      <c r="M154" s="9" t="n"/>
+      <c r="N154" s="9" t="n"/>
+      <c r="O154" s="9" t="n"/>
+      <c r="P154" s="9" t="n"/>
+      <c r="Q154" s="9" t="n"/>
+      <c r="R154" s="9" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="2" t="n"/>
+      <c r="A155" s="9" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="9" t="n"/>
+      <c r="G155" s="15" t="n"/>
+      <c r="H155" s="15">
+        <f>IF(G155="","",E155-G155)</f>
+        <v/>
+      </c>
+      <c r="I155" s="9">
+        <f>IF(AND(F155="available",G155&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H155)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J155" s="9" t="n"/>
+      <c r="K155" s="9" t="n"/>
+      <c r="L155" s="9" t="n"/>
+      <c r="M155" s="9" t="n"/>
+      <c r="N155" s="9" t="n"/>
+      <c r="O155" s="9" t="n"/>
+      <c r="P155" s="9" t="n"/>
+      <c r="Q155" s="9" t="n"/>
+      <c r="R155" s="9" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="2" t="n"/>
+      <c r="A156" s="9" t="n"/>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="9" t="n"/>
+      <c r="D156" s="10" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="9" t="n"/>
+      <c r="G156" s="15" t="n"/>
+      <c r="H156" s="15">
+        <f>IF(G156="","",E156-G156)</f>
+        <v/>
+      </c>
+      <c r="I156" s="9">
+        <f>IF(AND(F156="available",G156&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H156)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J156" s="9" t="n"/>
+      <c r="K156" s="9" t="n"/>
+      <c r="L156" s="9" t="n"/>
+      <c r="M156" s="9" t="n"/>
+      <c r="N156" s="9" t="n"/>
+      <c r="O156" s="9" t="n"/>
+      <c r="P156" s="9" t="n"/>
+      <c r="Q156" s="9" t="n"/>
+      <c r="R156" s="9" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="2" t="n"/>
+      <c r="A157" s="9" t="n"/>
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="9" t="n"/>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="9" t="n"/>
+      <c r="F157" s="9" t="n"/>
+      <c r="G157" s="15" t="n"/>
+      <c r="H157" s="15">
+        <f>IF(G157="","",E157-G157)</f>
+        <v/>
+      </c>
+      <c r="I157" s="9">
+        <f>IF(AND(F157="available",G157&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H157)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J157" s="9" t="n"/>
+      <c r="K157" s="9" t="n"/>
+      <c r="L157" s="9" t="n"/>
+      <c r="M157" s="9" t="n"/>
+      <c r="N157" s="9" t="n"/>
+      <c r="O157" s="9" t="n"/>
+      <c r="P157" s="9" t="n"/>
+      <c r="Q157" s="9" t="n"/>
+      <c r="R157" s="9" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="2" t="n"/>
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="10" t="n"/>
+      <c r="E158" s="9" t="n"/>
+      <c r="F158" s="9" t="n"/>
+      <c r="G158" s="15" t="n"/>
+      <c r="H158" s="15">
+        <f>IF(G158="","",E158-G158)</f>
+        <v/>
+      </c>
+      <c r="I158" s="9">
+        <f>IF(AND(F158="available",G158&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H158)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J158" s="9" t="n"/>
+      <c r="K158" s="9" t="n"/>
+      <c r="L158" s="9" t="n"/>
+      <c r="M158" s="9" t="n"/>
+      <c r="N158" s="9" t="n"/>
+      <c r="O158" s="9" t="n"/>
+      <c r="P158" s="9" t="n"/>
+      <c r="Q158" s="9" t="n"/>
+      <c r="R158" s="9" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="2" t="n"/>
+      <c r="A159" s="9" t="n"/>
+      <c r="B159" s="9" t="n"/>
+      <c r="C159" s="9" t="n"/>
+      <c r="D159" s="10" t="n"/>
+      <c r="E159" s="9" t="n"/>
+      <c r="F159" s="9" t="n"/>
+      <c r="G159" s="15" t="n"/>
+      <c r="H159" s="15">
+        <f>IF(G159="","",E159-G159)</f>
+        <v/>
+      </c>
+      <c r="I159" s="9">
+        <f>IF(AND(F159="available",G159&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H159)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J159" s="9" t="n"/>
+      <c r="K159" s="9" t="n"/>
+      <c r="L159" s="9" t="n"/>
+      <c r="M159" s="9" t="n"/>
+      <c r="N159" s="9" t="n"/>
+      <c r="O159" s="9" t="n"/>
+      <c r="P159" s="9" t="n"/>
+      <c r="Q159" s="9" t="n"/>
+      <c r="R159" s="9" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="2" t="n"/>
+      <c r="A160" s="9" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="15" t="n"/>
+      <c r="H160" s="15">
+        <f>IF(G160="","",E160-G160)</f>
+        <v/>
+      </c>
+      <c r="I160" s="9">
+        <f>IF(AND(F160="available",G160&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H160)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J160" s="9" t="n"/>
+      <c r="K160" s="9" t="n"/>
+      <c r="L160" s="9" t="n"/>
+      <c r="M160" s="9" t="n"/>
+      <c r="N160" s="9" t="n"/>
+      <c r="O160" s="9" t="n"/>
+      <c r="P160" s="9" t="n"/>
+      <c r="Q160" s="9" t="n"/>
+      <c r="R160" s="9" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="2" t="n"/>
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="9" t="n"/>
+      <c r="D161" s="10" t="n"/>
+      <c r="E161" s="9" t="n"/>
+      <c r="F161" s="9" t="n"/>
+      <c r="G161" s="15" t="n"/>
+      <c r="H161" s="15">
+        <f>IF(G161="","",E161-G161)</f>
+        <v/>
+      </c>
+      <c r="I161" s="9">
+        <f>IF(AND(F161="available",G161&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H161)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J161" s="9" t="n"/>
+      <c r="K161" s="9" t="n"/>
+      <c r="L161" s="9" t="n"/>
+      <c r="M161" s="9" t="n"/>
+      <c r="N161" s="9" t="n"/>
+      <c r="O161" s="9" t="n"/>
+      <c r="P161" s="9" t="n"/>
+      <c r="Q161" s="9" t="n"/>
+      <c r="R161" s="9" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="2" t="n"/>
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="15" t="n"/>
+      <c r="H162" s="15">
+        <f>IF(G162="","",E162-G162)</f>
+        <v/>
+      </c>
+      <c r="I162" s="9">
+        <f>IF(AND(F162="available",G162&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H162)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J162" s="9" t="n"/>
+      <c r="K162" s="9" t="n"/>
+      <c r="L162" s="9" t="n"/>
+      <c r="M162" s="9" t="n"/>
+      <c r="N162" s="9" t="n"/>
+      <c r="O162" s="9" t="n"/>
+      <c r="P162" s="9" t="n"/>
+      <c r="Q162" s="9" t="n"/>
+      <c r="R162" s="9" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="2" t="n"/>
+      <c r="A163" s="9" t="n"/>
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
+      <c r="G163" s="15" t="n"/>
+      <c r="H163" s="15">
+        <f>IF(G163="","",E163-G163)</f>
+        <v/>
+      </c>
+      <c r="I163" s="9">
+        <f>IF(AND(F163="available",G163&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H163)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J163" s="9" t="n"/>
+      <c r="K163" s="9" t="n"/>
+      <c r="L163" s="9" t="n"/>
+      <c r="M163" s="9" t="n"/>
+      <c r="N163" s="9" t="n"/>
+      <c r="O163" s="9" t="n"/>
+      <c r="P163" s="9" t="n"/>
+      <c r="Q163" s="9" t="n"/>
+      <c r="R163" s="9" t="n"/>
     </row>
     <row r="164">
-      <c r="D164" s="2" t="n"/>
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="9" t="n"/>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="9" t="n"/>
+      <c r="F164" s="9" t="n"/>
+      <c r="G164" s="15" t="n"/>
+      <c r="H164" s="15">
+        <f>IF(G164="","",E164-G164)</f>
+        <v/>
+      </c>
+      <c r="I164" s="9">
+        <f>IF(AND(F164="available",G164&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H164)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J164" s="9" t="n"/>
+      <c r="K164" s="9" t="n"/>
+      <c r="L164" s="9" t="n"/>
+      <c r="M164" s="9" t="n"/>
+      <c r="N164" s="9" t="n"/>
+      <c r="O164" s="9" t="n"/>
+      <c r="P164" s="9" t="n"/>
+      <c r="Q164" s="9" t="n"/>
+      <c r="R164" s="9" t="n"/>
     </row>
     <row r="165">
-      <c r="D165" s="2" t="n"/>
+      <c r="A165" s="9" t="n"/>
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="9" t="n"/>
+      <c r="D165" s="10" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="15" t="n"/>
+      <c r="H165" s="15">
+        <f>IF(G165="","",E165-G165)</f>
+        <v/>
+      </c>
+      <c r="I165" s="9">
+        <f>IF(AND(F165="available",G165&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H165)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J165" s="9" t="n"/>
+      <c r="K165" s="9" t="n"/>
+      <c r="L165" s="9" t="n"/>
+      <c r="M165" s="9" t="n"/>
+      <c r="N165" s="9" t="n"/>
+      <c r="O165" s="9" t="n"/>
+      <c r="P165" s="9" t="n"/>
+      <c r="Q165" s="9" t="n"/>
+      <c r="R165" s="9" t="n"/>
     </row>
     <row r="166">
-      <c r="D166" s="2" t="n"/>
+      <c r="A166" s="9" t="n"/>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="15" t="n"/>
+      <c r="H166" s="15">
+        <f>IF(G166="","",E166-G166)</f>
+        <v/>
+      </c>
+      <c r="I166" s="9">
+        <f>IF(AND(F166="available",G166&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H166)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J166" s="9" t="n"/>
+      <c r="K166" s="9" t="n"/>
+      <c r="L166" s="9" t="n"/>
+      <c r="M166" s="9" t="n"/>
+      <c r="N166" s="9" t="n"/>
+      <c r="O166" s="9" t="n"/>
+      <c r="P166" s="9" t="n"/>
+      <c r="Q166" s="9" t="n"/>
+      <c r="R166" s="9" t="n"/>
     </row>
     <row r="167">
-      <c r="D167" s="2" t="n"/>
+      <c r="A167" s="9" t="n"/>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="9" t="n"/>
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="15" t="n"/>
+      <c r="H167" s="15">
+        <f>IF(G167="","",E167-G167)</f>
+        <v/>
+      </c>
+      <c r="I167" s="9">
+        <f>IF(AND(F167="available",G167&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H167)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J167" s="9" t="n"/>
+      <c r="K167" s="9" t="n"/>
+      <c r="L167" s="9" t="n"/>
+      <c r="M167" s="9" t="n"/>
+      <c r="N167" s="9" t="n"/>
+      <c r="O167" s="9" t="n"/>
+      <c r="P167" s="9" t="n"/>
+      <c r="Q167" s="9" t="n"/>
+      <c r="R167" s="9" t="n"/>
     </row>
     <row r="168">
-      <c r="D168" s="2" t="n"/>
+      <c r="A168" s="9" t="n"/>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="9" t="n"/>
+      <c r="D168" s="10" t="n"/>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="n"/>
+      <c r="G168" s="15" t="n"/>
+      <c r="H168" s="15">
+        <f>IF(G168="","",E168-G168)</f>
+        <v/>
+      </c>
+      <c r="I168" s="9">
+        <f>IF(AND(F168="available",G168&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H168)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J168" s="9" t="n"/>
+      <c r="K168" s="9" t="n"/>
+      <c r="L168" s="9" t="n"/>
+      <c r="M168" s="9" t="n"/>
+      <c r="N168" s="9" t="n"/>
+      <c r="O168" s="9" t="n"/>
+      <c r="P168" s="9" t="n"/>
+      <c r="Q168" s="9" t="n"/>
+      <c r="R168" s="9" t="n"/>
     </row>
     <row r="169">
-      <c r="D169" s="2" t="n"/>
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="10" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="15" t="n"/>
+      <c r="H169" s="15">
+        <f>IF(G169="","",E169-G169)</f>
+        <v/>
+      </c>
+      <c r="I169" s="9">
+        <f>IF(AND(F169="available",G169&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H169)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J169" s="9" t="n"/>
+      <c r="K169" s="9" t="n"/>
+      <c r="L169" s="9" t="n"/>
+      <c r="M169" s="9" t="n"/>
+      <c r="N169" s="9" t="n"/>
+      <c r="O169" s="9" t="n"/>
+      <c r="P169" s="9" t="n"/>
+      <c r="Q169" s="9" t="n"/>
+      <c r="R169" s="9" t="n"/>
     </row>
     <row r="170">
-      <c r="D170" s="2" t="n"/>
+      <c r="A170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="9" t="n"/>
+      <c r="G170" s="15" t="n"/>
+      <c r="H170" s="15">
+        <f>IF(G170="","",E170-G170)</f>
+        <v/>
+      </c>
+      <c r="I170" s="9">
+        <f>IF(AND(F170="available",G170&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H170)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J170" s="9" t="n"/>
+      <c r="K170" s="9" t="n"/>
+      <c r="L170" s="9" t="n"/>
+      <c r="M170" s="9" t="n"/>
+      <c r="N170" s="9" t="n"/>
+      <c r="O170" s="9" t="n"/>
+      <c r="P170" s="9" t="n"/>
+      <c r="Q170" s="9" t="n"/>
+      <c r="R170" s="9" t="n"/>
     </row>
     <row r="171">
-      <c r="D171" s="2" t="n"/>
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="9" t="n"/>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="9" t="n"/>
+      <c r="F171" s="9" t="n"/>
+      <c r="G171" s="15" t="n"/>
+      <c r="H171" s="15">
+        <f>IF(G171="","",E171-G171)</f>
+        <v/>
+      </c>
+      <c r="I171" s="9">
+        <f>IF(AND(F171="available",G171&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H171)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J171" s="9" t="n"/>
+      <c r="K171" s="9" t="n"/>
+      <c r="L171" s="9" t="n"/>
+      <c r="M171" s="9" t="n"/>
+      <c r="N171" s="9" t="n"/>
+      <c r="O171" s="9" t="n"/>
+      <c r="P171" s="9" t="n"/>
+      <c r="Q171" s="9" t="n"/>
+      <c r="R171" s="9" t="n"/>
     </row>
     <row r="172">
-      <c r="D172" s="2" t="n"/>
+      <c r="A172" s="9" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="10" t="n"/>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="15" t="n"/>
+      <c r="H172" s="15">
+        <f>IF(G172="","",E172-G172)</f>
+        <v/>
+      </c>
+      <c r="I172" s="9">
+        <f>IF(AND(F172="available",G172&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H172)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J172" s="9" t="n"/>
+      <c r="K172" s="9" t="n"/>
+      <c r="L172" s="9" t="n"/>
+      <c r="M172" s="9" t="n"/>
+      <c r="N172" s="9" t="n"/>
+      <c r="O172" s="9" t="n"/>
+      <c r="P172" s="9" t="n"/>
+      <c r="Q172" s="9" t="n"/>
+      <c r="R172" s="9" t="n"/>
     </row>
     <row r="173">
-      <c r="D173" s="2" t="n"/>
+      <c r="A173" s="9" t="n"/>
+      <c r="B173" s="9" t="n"/>
+      <c r="C173" s="9" t="n"/>
+      <c r="D173" s="10" t="n"/>
+      <c r="E173" s="9" t="n"/>
+      <c r="F173" s="9" t="n"/>
+      <c r="G173" s="15" t="n"/>
+      <c r="H173" s="15">
+        <f>IF(G173="","",E173-G173)</f>
+        <v/>
+      </c>
+      <c r="I173" s="9">
+        <f>IF(AND(F173="available",G173&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H173)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J173" s="9" t="n"/>
+      <c r="K173" s="9" t="n"/>
+      <c r="L173" s="9" t="n"/>
+      <c r="M173" s="9" t="n"/>
+      <c r="N173" s="9" t="n"/>
+      <c r="O173" s="9" t="n"/>
+      <c r="P173" s="9" t="n"/>
+      <c r="Q173" s="9" t="n"/>
+      <c r="R173" s="9" t="n"/>
     </row>
     <row r="174">
-      <c r="D174" s="2" t="n"/>
+      <c r="A174" s="9" t="n"/>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="10" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="15" t="n"/>
+      <c r="H174" s="15">
+        <f>IF(G174="","",E174-G174)</f>
+        <v/>
+      </c>
+      <c r="I174" s="9">
+        <f>IF(AND(F174="available",G174&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H174)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J174" s="9" t="n"/>
+      <c r="K174" s="9" t="n"/>
+      <c r="L174" s="9" t="n"/>
+      <c r="M174" s="9" t="n"/>
+      <c r="N174" s="9" t="n"/>
+      <c r="O174" s="9" t="n"/>
+      <c r="P174" s="9" t="n"/>
+      <c r="Q174" s="9" t="n"/>
+      <c r="R174" s="9" t="n"/>
     </row>
     <row r="175">
-      <c r="D175" s="2" t="n"/>
+      <c r="A175" s="9" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="9" t="n"/>
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="9" t="n"/>
+      <c r="F175" s="9" t="n"/>
+      <c r="G175" s="15" t="n"/>
+      <c r="H175" s="15">
+        <f>IF(G175="","",E175-G175)</f>
+        <v/>
+      </c>
+      <c r="I175" s="9">
+        <f>IF(AND(F175="available",G175&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H175)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J175" s="9" t="n"/>
+      <c r="K175" s="9" t="n"/>
+      <c r="L175" s="9" t="n"/>
+      <c r="M175" s="9" t="n"/>
+      <c r="N175" s="9" t="n"/>
+      <c r="O175" s="9" t="n"/>
+      <c r="P175" s="9" t="n"/>
+      <c r="Q175" s="9" t="n"/>
+      <c r="R175" s="9" t="n"/>
     </row>
     <row r="176">
-      <c r="D176" s="2" t="n"/>
+      <c r="A176" s="9" t="n"/>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="9" t="n"/>
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="9" t="n"/>
+      <c r="F176" s="9" t="n"/>
+      <c r="G176" s="15" t="n"/>
+      <c r="H176" s="15">
+        <f>IF(G176="","",E176-G176)</f>
+        <v/>
+      </c>
+      <c r="I176" s="9">
+        <f>IF(AND(F176="available",G176&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H176)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J176" s="9" t="n"/>
+      <c r="K176" s="9" t="n"/>
+      <c r="L176" s="9" t="n"/>
+      <c r="M176" s="9" t="n"/>
+      <c r="N176" s="9" t="n"/>
+      <c r="O176" s="9" t="n"/>
+      <c r="P176" s="9" t="n"/>
+      <c r="Q176" s="9" t="n"/>
+      <c r="R176" s="9" t="n"/>
     </row>
     <row r="177">
-      <c r="D177" s="2" t="n"/>
+      <c r="A177" s="9" t="n"/>
+      <c r="B177" s="9" t="n"/>
+      <c r="C177" s="9" t="n"/>
+      <c r="D177" s="10" t="n"/>
+      <c r="E177" s="9" t="n"/>
+      <c r="F177" s="9" t="n"/>
+      <c r="G177" s="15" t="n"/>
+      <c r="H177" s="15">
+        <f>IF(G177="","",E177-G177)</f>
+        <v/>
+      </c>
+      <c r="I177" s="9">
+        <f>IF(AND(F177="available",G177&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H177)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J177" s="9" t="n"/>
+      <c r="K177" s="9" t="n"/>
+      <c r="L177" s="9" t="n"/>
+      <c r="M177" s="9" t="n"/>
+      <c r="N177" s="9" t="n"/>
+      <c r="O177" s="9" t="n"/>
+      <c r="P177" s="9" t="n"/>
+      <c r="Q177" s="9" t="n"/>
+      <c r="R177" s="9" t="n"/>
     </row>
     <row r="178">
-      <c r="D178" s="2" t="n"/>
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="9" t="n"/>
+      <c r="D178" s="10" t="n"/>
+      <c r="E178" s="9" t="n"/>
+      <c r="F178" s="9" t="n"/>
+      <c r="G178" s="15" t="n"/>
+      <c r="H178" s="15">
+        <f>IF(G178="","",E178-G178)</f>
+        <v/>
+      </c>
+      <c r="I178" s="9">
+        <f>IF(AND(F178="available",G178&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H178)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J178" s="9" t="n"/>
+      <c r="K178" s="9" t="n"/>
+      <c r="L178" s="9" t="n"/>
+      <c r="M178" s="9" t="n"/>
+      <c r="N178" s="9" t="n"/>
+      <c r="O178" s="9" t="n"/>
+      <c r="P178" s="9" t="n"/>
+      <c r="Q178" s="9" t="n"/>
+      <c r="R178" s="9" t="n"/>
     </row>
     <row r="179">
-      <c r="D179" s="2" t="n"/>
+      <c r="A179" s="9" t="n"/>
+      <c r="B179" s="9" t="n"/>
+      <c r="C179" s="9" t="n"/>
+      <c r="D179" s="10" t="n"/>
+      <c r="E179" s="9" t="n"/>
+      <c r="F179" s="9" t="n"/>
+      <c r="G179" s="15" t="n"/>
+      <c r="H179" s="15">
+        <f>IF(G179="","",E179-G179)</f>
+        <v/>
+      </c>
+      <c r="I179" s="9">
+        <f>IF(AND(F179="available",G179&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H179)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J179" s="9" t="n"/>
+      <c r="K179" s="9" t="n"/>
+      <c r="L179" s="9" t="n"/>
+      <c r="M179" s="9" t="n"/>
+      <c r="N179" s="9" t="n"/>
+      <c r="O179" s="9" t="n"/>
+      <c r="P179" s="9" t="n"/>
+      <c r="Q179" s="9" t="n"/>
+      <c r="R179" s="9" t="n"/>
     </row>
     <row r="180">
-      <c r="D180" s="2" t="n"/>
+      <c r="A180" s="9" t="n"/>
+      <c r="B180" s="9" t="n"/>
+      <c r="C180" s="9" t="n"/>
+      <c r="D180" s="10" t="n"/>
+      <c r="E180" s="9" t="n"/>
+      <c r="F180" s="9" t="n"/>
+      <c r="G180" s="15" t="n"/>
+      <c r="H180" s="15">
+        <f>IF(G180="","",E180-G180)</f>
+        <v/>
+      </c>
+      <c r="I180" s="9">
+        <f>IF(AND(F180="available",G180&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H180)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J180" s="9" t="n"/>
+      <c r="K180" s="9" t="n"/>
+      <c r="L180" s="9" t="n"/>
+      <c r="M180" s="9" t="n"/>
+      <c r="N180" s="9" t="n"/>
+      <c r="O180" s="9" t="n"/>
+      <c r="P180" s="9" t="n"/>
+      <c r="Q180" s="9" t="n"/>
+      <c r="R180" s="9" t="n"/>
     </row>
     <row r="181">
-      <c r="D181" s="2" t="n"/>
+      <c r="A181" s="9" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="10" t="n"/>
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="9" t="n"/>
+      <c r="G181" s="15" t="n"/>
+      <c r="H181" s="15">
+        <f>IF(G181="","",E181-G181)</f>
+        <v/>
+      </c>
+      <c r="I181" s="9">
+        <f>IF(AND(F181="available",G181&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H181)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J181" s="9" t="n"/>
+      <c r="K181" s="9" t="n"/>
+      <c r="L181" s="9" t="n"/>
+      <c r="M181" s="9" t="n"/>
+      <c r="N181" s="9" t="n"/>
+      <c r="O181" s="9" t="n"/>
+      <c r="P181" s="9" t="n"/>
+      <c r="Q181" s="9" t="n"/>
+      <c r="R181" s="9" t="n"/>
     </row>
     <row r="182">
-      <c r="D182" s="2" t="n"/>
+      <c r="A182" s="9" t="n"/>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="9" t="n"/>
+      <c r="D182" s="10" t="n"/>
+      <c r="E182" s="9" t="n"/>
+      <c r="F182" s="9" t="n"/>
+      <c r="G182" s="15" t="n"/>
+      <c r="H182" s="15">
+        <f>IF(G182="","",E182-G182)</f>
+        <v/>
+      </c>
+      <c r="I182" s="9">
+        <f>IF(AND(F182="available",G182&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H182)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J182" s="9" t="n"/>
+      <c r="K182" s="9" t="n"/>
+      <c r="L182" s="9" t="n"/>
+      <c r="M182" s="9" t="n"/>
+      <c r="N182" s="9" t="n"/>
+      <c r="O182" s="9" t="n"/>
+      <c r="P182" s="9" t="n"/>
+      <c r="Q182" s="9" t="n"/>
+      <c r="R182" s="9" t="n"/>
     </row>
     <row r="183">
-      <c r="D183" s="2" t="n"/>
+      <c r="A183" s="9" t="n"/>
+      <c r="B183" s="9" t="n"/>
+      <c r="C183" s="9" t="n"/>
+      <c r="D183" s="10" t="n"/>
+      <c r="E183" s="9" t="n"/>
+      <c r="F183" s="9" t="n"/>
+      <c r="G183" s="15" t="n"/>
+      <c r="H183" s="15">
+        <f>IF(G183="","",E183-G183)</f>
+        <v/>
+      </c>
+      <c r="I183" s="9">
+        <f>IF(AND(F183="available",G183&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H183)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J183" s="9" t="n"/>
+      <c r="K183" s="9" t="n"/>
+      <c r="L183" s="9" t="n"/>
+      <c r="M183" s="9" t="n"/>
+      <c r="N183" s="9" t="n"/>
+      <c r="O183" s="9" t="n"/>
+      <c r="P183" s="9" t="n"/>
+      <c r="Q183" s="9" t="n"/>
+      <c r="R183" s="9" t="n"/>
     </row>
     <row r="184">
-      <c r="D184" s="2" t="n"/>
+      <c r="A184" s="9" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="10" t="n"/>
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
+      <c r="G184" s="15" t="n"/>
+      <c r="H184" s="15">
+        <f>IF(G184="","",E184-G184)</f>
+        <v/>
+      </c>
+      <c r="I184" s="9">
+        <f>IF(AND(F184="available",G184&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H184)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J184" s="9" t="n"/>
+      <c r="K184" s="9" t="n"/>
+      <c r="L184" s="9" t="n"/>
+      <c r="M184" s="9" t="n"/>
+      <c r="N184" s="9" t="n"/>
+      <c r="O184" s="9" t="n"/>
+      <c r="P184" s="9" t="n"/>
+      <c r="Q184" s="9" t="n"/>
+      <c r="R184" s="9" t="n"/>
     </row>
     <row r="185">
-      <c r="D185" s="2" t="n"/>
+      <c r="A185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="9" t="n"/>
+      <c r="D185" s="10" t="n"/>
+      <c r="E185" s="9" t="n"/>
+      <c r="F185" s="9" t="n"/>
+      <c r="G185" s="15" t="n"/>
+      <c r="H185" s="15">
+        <f>IF(G185="","",E185-G185)</f>
+        <v/>
+      </c>
+      <c r="I185" s="9">
+        <f>IF(AND(F185="available",G185&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H185)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J185" s="9" t="n"/>
+      <c r="K185" s="9" t="n"/>
+      <c r="L185" s="9" t="n"/>
+      <c r="M185" s="9" t="n"/>
+      <c r="N185" s="9" t="n"/>
+      <c r="O185" s="9" t="n"/>
+      <c r="P185" s="9" t="n"/>
+      <c r="Q185" s="9" t="n"/>
+      <c r="R185" s="9" t="n"/>
     </row>
     <row r="186">
-      <c r="D186" s="2" t="n"/>
+      <c r="A186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="9" t="n"/>
+      <c r="D186" s="10" t="n"/>
+      <c r="E186" s="9" t="n"/>
+      <c r="F186" s="9" t="n"/>
+      <c r="G186" s="15" t="n"/>
+      <c r="H186" s="15">
+        <f>IF(G186="","",E186-G186)</f>
+        <v/>
+      </c>
+      <c r="I186" s="9">
+        <f>IF(AND(F186="available",G186&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H186)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J186" s="9" t="n"/>
+      <c r="K186" s="9" t="n"/>
+      <c r="L186" s="9" t="n"/>
+      <c r="M186" s="9" t="n"/>
+      <c r="N186" s="9" t="n"/>
+      <c r="O186" s="9" t="n"/>
+      <c r="P186" s="9" t="n"/>
+      <c r="Q186" s="9" t="n"/>
+      <c r="R186" s="9" t="n"/>
     </row>
     <row r="187">
-      <c r="D187" s="2" t="n"/>
+      <c r="A187" s="9" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="9" t="n"/>
+      <c r="D187" s="10" t="n"/>
+      <c r="E187" s="9" t="n"/>
+      <c r="F187" s="9" t="n"/>
+      <c r="G187" s="15" t="n"/>
+      <c r="H187" s="15">
+        <f>IF(G187="","",E187-G187)</f>
+        <v/>
+      </c>
+      <c r="I187" s="9">
+        <f>IF(AND(F187="available",G187&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H187)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J187" s="9" t="n"/>
+      <c r="K187" s="9" t="n"/>
+      <c r="L187" s="9" t="n"/>
+      <c r="M187" s="9" t="n"/>
+      <c r="N187" s="9" t="n"/>
+      <c r="O187" s="9" t="n"/>
+      <c r="P187" s="9" t="n"/>
+      <c r="Q187" s="9" t="n"/>
+      <c r="R187" s="9" t="n"/>
     </row>
     <row r="188">
-      <c r="D188" s="2" t="n"/>
+      <c r="A188" s="9" t="n"/>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="9" t="n"/>
+      <c r="D188" s="10" t="n"/>
+      <c r="E188" s="9" t="n"/>
+      <c r="F188" s="9" t="n"/>
+      <c r="G188" s="15" t="n"/>
+      <c r="H188" s="15">
+        <f>IF(G188="","",E188-G188)</f>
+        <v/>
+      </c>
+      <c r="I188" s="9">
+        <f>IF(AND(F188="available",G188&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H188)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J188" s="9" t="n"/>
+      <c r="K188" s="9" t="n"/>
+      <c r="L188" s="9" t="n"/>
+      <c r="M188" s="9" t="n"/>
+      <c r="N188" s="9" t="n"/>
+      <c r="O188" s="9" t="n"/>
+      <c r="P188" s="9" t="n"/>
+      <c r="Q188" s="9" t="n"/>
+      <c r="R188" s="9" t="n"/>
     </row>
     <row r="189">
-      <c r="D189" s="2" t="n"/>
+      <c r="A189" s="9" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="9" t="n"/>
+      <c r="D189" s="10" t="n"/>
+      <c r="E189" s="9" t="n"/>
+      <c r="F189" s="9" t="n"/>
+      <c r="G189" s="15" t="n"/>
+      <c r="H189" s="15">
+        <f>IF(G189="","",E189-G189)</f>
+        <v/>
+      </c>
+      <c r="I189" s="9">
+        <f>IF(AND(F189="available",G189&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H189)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J189" s="9" t="n"/>
+      <c r="K189" s="9" t="n"/>
+      <c r="L189" s="9" t="n"/>
+      <c r="M189" s="9" t="n"/>
+      <c r="N189" s="9" t="n"/>
+      <c r="O189" s="9" t="n"/>
+      <c r="P189" s="9" t="n"/>
+      <c r="Q189" s="9" t="n"/>
+      <c r="R189" s="9" t="n"/>
     </row>
     <row r="190">
-      <c r="D190" s="2" t="n"/>
+      <c r="A190" s="9" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="9" t="n"/>
+      <c r="D190" s="10" t="n"/>
+      <c r="E190" s="9" t="n"/>
+      <c r="F190" s="9" t="n"/>
+      <c r="G190" s="15" t="n"/>
+      <c r="H190" s="15">
+        <f>IF(G190="","",E190-G190)</f>
+        <v/>
+      </c>
+      <c r="I190" s="9">
+        <f>IF(AND(F190="available",G190&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H190)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J190" s="9" t="n"/>
+      <c r="K190" s="9" t="n"/>
+      <c r="L190" s="9" t="n"/>
+      <c r="M190" s="9" t="n"/>
+      <c r="N190" s="9" t="n"/>
+      <c r="O190" s="9" t="n"/>
+      <c r="P190" s="9" t="n"/>
+      <c r="Q190" s="9" t="n"/>
+      <c r="R190" s="9" t="n"/>
     </row>
     <row r="191">
-      <c r="D191" s="2" t="n"/>
+      <c r="A191" s="9" t="n"/>
+      <c r="B191" s="9" t="n"/>
+      <c r="C191" s="9" t="n"/>
+      <c r="D191" s="10" t="n"/>
+      <c r="E191" s="9" t="n"/>
+      <c r="F191" s="9" t="n"/>
+      <c r="G191" s="15" t="n"/>
+      <c r="H191" s="15">
+        <f>IF(G191="","",E191-G191)</f>
+        <v/>
+      </c>
+      <c r="I191" s="9">
+        <f>IF(AND(F191="available",G191&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H191)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J191" s="9" t="n"/>
+      <c r="K191" s="9" t="n"/>
+      <c r="L191" s="9" t="n"/>
+      <c r="M191" s="9" t="n"/>
+      <c r="N191" s="9" t="n"/>
+      <c r="O191" s="9" t="n"/>
+      <c r="P191" s="9" t="n"/>
+      <c r="Q191" s="9" t="n"/>
+      <c r="R191" s="9" t="n"/>
     </row>
     <row r="192">
-      <c r="D192" s="2" t="n"/>
+      <c r="A192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="9" t="n"/>
+      <c r="D192" s="10" t="n"/>
+      <c r="E192" s="9" t="n"/>
+      <c r="F192" s="9" t="n"/>
+      <c r="G192" s="15" t="n"/>
+      <c r="H192" s="15">
+        <f>IF(G192="","",E192-G192)</f>
+        <v/>
+      </c>
+      <c r="I192" s="9">
+        <f>IF(AND(F192="available",G192&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H192)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J192" s="9" t="n"/>
+      <c r="K192" s="9" t="n"/>
+      <c r="L192" s="9" t="n"/>
+      <c r="M192" s="9" t="n"/>
+      <c r="N192" s="9" t="n"/>
+      <c r="O192" s="9" t="n"/>
+      <c r="P192" s="9" t="n"/>
+      <c r="Q192" s="9" t="n"/>
+      <c r="R192" s="9" t="n"/>
     </row>
     <row r="193">
-      <c r="D193" s="2" t="n"/>
+      <c r="A193" s="9" t="n"/>
+      <c r="B193" s="9" t="n"/>
+      <c r="C193" s="9" t="n"/>
+      <c r="D193" s="10" t="n"/>
+      <c r="E193" s="9" t="n"/>
+      <c r="F193" s="9" t="n"/>
+      <c r="G193" s="15" t="n"/>
+      <c r="H193" s="15">
+        <f>IF(G193="","",E193-G193)</f>
+        <v/>
+      </c>
+      <c r="I193" s="9">
+        <f>IF(AND(F193="available",G193&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H193)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J193" s="9" t="n"/>
+      <c r="K193" s="9" t="n"/>
+      <c r="L193" s="9" t="n"/>
+      <c r="M193" s="9" t="n"/>
+      <c r="N193" s="9" t="n"/>
+      <c r="O193" s="9" t="n"/>
+      <c r="P193" s="9" t="n"/>
+      <c r="Q193" s="9" t="n"/>
+      <c r="R193" s="9" t="n"/>
     </row>
     <row r="194">
-      <c r="D194" s="2" t="n"/>
+      <c r="A194" s="9" t="n"/>
+      <c r="B194" s="9" t="n"/>
+      <c r="C194" s="9" t="n"/>
+      <c r="D194" s="10" t="n"/>
+      <c r="E194" s="9" t="n"/>
+      <c r="F194" s="9" t="n"/>
+      <c r="G194" s="15" t="n"/>
+      <c r="H194" s="15">
+        <f>IF(G194="","",E194-G194)</f>
+        <v/>
+      </c>
+      <c r="I194" s="9">
+        <f>IF(AND(F194="available",G194&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H194)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J194" s="9" t="n"/>
+      <c r="K194" s="9" t="n"/>
+      <c r="L194" s="9" t="n"/>
+      <c r="M194" s="9" t="n"/>
+      <c r="N194" s="9" t="n"/>
+      <c r="O194" s="9" t="n"/>
+      <c r="P194" s="9" t="n"/>
+      <c r="Q194" s="9" t="n"/>
+      <c r="R194" s="9" t="n"/>
     </row>
     <row r="195">
-      <c r="D195" s="2" t="n"/>
+      <c r="A195" s="9" t="n"/>
+      <c r="B195" s="9" t="n"/>
+      <c r="C195" s="9" t="n"/>
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="9" t="n"/>
+      <c r="F195" s="9" t="n"/>
+      <c r="G195" s="15" t="n"/>
+      <c r="H195" s="15">
+        <f>IF(G195="","",E195-G195)</f>
+        <v/>
+      </c>
+      <c r="I195" s="9">
+        <f>IF(AND(F195="available",G195&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H195)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J195" s="9" t="n"/>
+      <c r="K195" s="9" t="n"/>
+      <c r="L195" s="9" t="n"/>
+      <c r="M195" s="9" t="n"/>
+      <c r="N195" s="9" t="n"/>
+      <c r="O195" s="9" t="n"/>
+      <c r="P195" s="9" t="n"/>
+      <c r="Q195" s="9" t="n"/>
+      <c r="R195" s="9" t="n"/>
     </row>
     <row r="196">
-      <c r="D196" s="2" t="n"/>
+      <c r="A196" s="9" t="n"/>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="10" t="n"/>
+      <c r="E196" s="9" t="n"/>
+      <c r="F196" s="9" t="n"/>
+      <c r="G196" s="15" t="n"/>
+      <c r="H196" s="15">
+        <f>IF(G196="","",E196-G196)</f>
+        <v/>
+      </c>
+      <c r="I196" s="9">
+        <f>IF(AND(F196="available",G196&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H196)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J196" s="9" t="n"/>
+      <c r="K196" s="9" t="n"/>
+      <c r="L196" s="9" t="n"/>
+      <c r="M196" s="9" t="n"/>
+      <c r="N196" s="9" t="n"/>
+      <c r="O196" s="9" t="n"/>
+      <c r="P196" s="9" t="n"/>
+      <c r="Q196" s="9" t="n"/>
+      <c r="R196" s="9" t="n"/>
     </row>
     <row r="197">
-      <c r="D197" s="2" t="n"/>
+      <c r="A197" s="9" t="n"/>
+      <c r="B197" s="9" t="n"/>
+      <c r="C197" s="9" t="n"/>
+      <c r="D197" s="10" t="n"/>
+      <c r="E197" s="9" t="n"/>
+      <c r="F197" s="9" t="n"/>
+      <c r="G197" s="15" t="n"/>
+      <c r="H197" s="15">
+        <f>IF(G197="","",E197-G197)</f>
+        <v/>
+      </c>
+      <c r="I197" s="9">
+        <f>IF(AND(F197="available",G197&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H197)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J197" s="9" t="n"/>
+      <c r="K197" s="9" t="n"/>
+      <c r="L197" s="9" t="n"/>
+      <c r="M197" s="9" t="n"/>
+      <c r="N197" s="9" t="n"/>
+      <c r="O197" s="9" t="n"/>
+      <c r="P197" s="9" t="n"/>
+      <c r="Q197" s="9" t="n"/>
+      <c r="R197" s="9" t="n"/>
     </row>
     <row r="198">
-      <c r="D198" s="2" t="n"/>
+      <c r="A198" s="9" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="10" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="15" t="n"/>
+      <c r="H198" s="15">
+        <f>IF(G198="","",E198-G198)</f>
+        <v/>
+      </c>
+      <c r="I198" s="9">
+        <f>IF(AND(F198="available",G198&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H198)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J198" s="9" t="n"/>
+      <c r="K198" s="9" t="n"/>
+      <c r="L198" s="9" t="n"/>
+      <c r="M198" s="9" t="n"/>
+      <c r="N198" s="9" t="n"/>
+      <c r="O198" s="9" t="n"/>
+      <c r="P198" s="9" t="n"/>
+      <c r="Q198" s="9" t="n"/>
+      <c r="R198" s="9" t="n"/>
     </row>
     <row r="199">
-      <c r="D199" s="2" t="n"/>
+      <c r="A199" s="9" t="n"/>
+      <c r="B199" s="9" t="n"/>
+      <c r="C199" s="9" t="n"/>
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="9" t="n"/>
+      <c r="F199" s="9" t="n"/>
+      <c r="G199" s="15" t="n"/>
+      <c r="H199" s="15">
+        <f>IF(G199="","",E199-G199)</f>
+        <v/>
+      </c>
+      <c r="I199" s="9">
+        <f>IF(AND(F199="available",G199&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H199)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J199" s="9" t="n"/>
+      <c r="K199" s="9" t="n"/>
+      <c r="L199" s="9" t="n"/>
+      <c r="M199" s="9" t="n"/>
+      <c r="N199" s="9" t="n"/>
+      <c r="O199" s="9" t="n"/>
+      <c r="P199" s="9" t="n"/>
+      <c r="Q199" s="9" t="n"/>
+      <c r="R199" s="9" t="n"/>
     </row>
     <row r="200">
-      <c r="D200" s="2" t="n"/>
+      <c r="A200" s="9" t="n"/>
+      <c r="B200" s="9" t="n"/>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="10" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
+      <c r="G200" s="15" t="n"/>
+      <c r="H200" s="15">
+        <f>IF(G200="","",E200-G200)</f>
+        <v/>
+      </c>
+      <c r="I200" s="9">
+        <f>IF(AND(F200="available",G200&lt;&gt;""),COUNTIFS($F$2:$F$200,"available",$H$2:$H$200,"&gt;"&amp;H200)&lt;$U$1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J200" s="9" t="n"/>
+      <c r="K200" s="9" t="n"/>
+      <c r="L200" s="9" t="n"/>
+      <c r="M200" s="9" t="n"/>
+      <c r="N200" s="9" t="n"/>
+      <c r="O200" s="9" t="n"/>
+      <c r="P200" s="9" t="n"/>
+      <c r="Q200" s="9" t="n"/>
+      <c r="R200" s="9" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R200"/>
+  <conditionalFormatting sqref="A2:F200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:R200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F200">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"available"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
+      <formula>"reserved"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
+      <formula>"sold"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
+      <formula>"shipped"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid status" error="Status must be one of: available, reserved, sold, shipped" type="list">
       <formula1>"available,reserved,sold,shipped"</formula1>
